--- a/inventory_updated.xlsx
+++ b/inventory_updated.xlsx
@@ -2,87 +2,91 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R684235f916774ac2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R2e357db775034ff8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="Ra477e9a311814f16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R3896a6417e884f83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="Rb5ecefa52c7148a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Rd2afd333faf04c12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R240ca43f52794154"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R4c32818c24d84965"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="Re6771774366f4d4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Rb8521a8a2ae54be9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R88041f53f8854032"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="R9020503632c44ec3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R9168e0353fd14d5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="R3ce9cdc9906743c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R1948457208924781"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="Rdf21801e635947f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="R881e26baf7394b45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R23a55a77abb64c56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="Rc0825105d29544ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="Rbacbe9076d5c4923"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="Rd91380ff158d4ca5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R131116d1169a4f1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R039a94a6c97940e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0045" sheetId="24" r:id="R5fc305edb48d4331"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0046" sheetId="25" r:id="Ra5fb633ab3024565"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0047" sheetId="26" r:id="Rd43934ea41c449ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0048" sheetId="27" r:id="Raa0f4b0a39db42f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0049" sheetId="28" r:id="R156b398f58894367"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0050" sheetId="29" r:id="Rf9290c5af9f34beb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0051" sheetId="30" r:id="Rb56ffe0413c44638"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0056" sheetId="31" r:id="R23684af4f38e4c48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0057" sheetId="32" r:id="Rae820af1bdab4a71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0058" sheetId="33" r:id="Rb22b5785b3324707"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0059" sheetId="34" r:id="R7166813d2ac24da9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0060" sheetId="35" r:id="R9c067c7513b84faa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0061" sheetId="36" r:id="Rb877919842a349ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0062" sheetId="37" r:id="Rbe71fad385eb48df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0052" sheetId="38" r:id="Rdcf230d360444f6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0053" sheetId="39" r:id="R1ccedd88da4f4c7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0054" sheetId="40" r:id="R5862cc58b67e471e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0055" sheetId="41" r:id="R63eaa5fd45654264"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0063" sheetId="42" r:id="Re9e63035ebd74c52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0064" sheetId="43" r:id="R4df10b7c3e2245cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0065" sheetId="44" r:id="Ra22a4c5ffdb7454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0066" sheetId="45" r:id="R4396a1e52bf24e5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0067" sheetId="46" r:id="R66dbbe9cd2a9455e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0068" sheetId="47" r:id="Rb3496810ac284fac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0069" sheetId="48" r:id="Reff5c93602e8468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0070" sheetId="49" r:id="Rc0512001bc184a3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0071" sheetId="50" r:id="R5d2463e060de423c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0072" sheetId="51" r:id="R72f1467af4024636"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0073" sheetId="52" r:id="R4d8726c402264570"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0074" sheetId="53" r:id="R0c821800514f4c9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0075" sheetId="54" r:id="R7df320c5637048d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0076" sheetId="55" r:id="R9fb9da0f97364101"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0077" sheetId="56" r:id="Rab44dfc56a0e483b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0078" sheetId="57" r:id="R69c9e39b004c454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0079" sheetId="58" r:id="R148e9d954fa842d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0080" sheetId="59" r:id="R3e082d9085fa4022"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0081" sheetId="60" r:id="R2825b5b8433d4933"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0082" sheetId="61" r:id="Rcc9fee8c4eb34bed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0083" sheetId="62" r:id="Ra7c5594276a54fe1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0084" sheetId="63" r:id="R5138d03a1fba4957"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0085" sheetId="64" r:id="R8115923b170343e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Directory" sheetId="65" r:id="R50d10a190ab14c89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0086" sheetId="66" r:id="R96e75e3492584fa1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0087" sheetId="67" r:id="Refef14c37dd94c19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0088" sheetId="68" r:id="Ra9f0723b461e4db9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0089" sheetId="69" r:id="R47b6971a4bd54036"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0090" sheetId="70" r:id="R65d60cd209674322"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0091" sheetId="71" r:id="Rd272bd60c1094b96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0092" sheetId="72" r:id="Rd1c248c5595e498c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0093" sheetId="73" r:id="R65ae8c122d1741e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0094" sheetId="74" r:id="Rb9d8457fd1b042e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0095" sheetId="75" r:id="R8c842c391de6460f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0096" sheetId="76" r:id="R898b7c22b3f2427c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0097" sheetId="77" r:id="R29d7ff172d604a0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0098" sheetId="78" r:id="R7fdaac0a4a9f42d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0099" sheetId="79" r:id="R41eaf07292e045d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0100" sheetId="80" r:id="Rcc8015fea922438d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0101" sheetId="81" r:id="R1f6969783ee6430a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R5fe6d4aa01074321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R38939fd0160942d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R678e66e2a2984380"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R1e466e309fbd4733"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R8a982de4c0094ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Rc75b103796c24a69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="Rafb398f1ae554e18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R553ec0ee894744cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R99ae12e442424832"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R59353b400ce74425"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="Rb508578561ad4f3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Rd9b89f6777ee49bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R299908abdcbd4e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Ra581628c61834cb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R7ee89cad2f45450c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="R09def91d42454b97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="R4b701289197a486e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R0f6c8cedc86f4d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="R9d6c10c2274f4d89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="Rf06952fa95db4d13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R6ff5ef97d9ce4d58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R7b556f34e80c4f58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R17aa46a75d444e1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0045" sheetId="24" r:id="R18cc8fc05cda441f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0046" sheetId="25" r:id="R55d8079d5c134737"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0047" sheetId="26" r:id="Rcdf077f56bd64719"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0048" sheetId="27" r:id="R6996ddd1ab3a4c3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0049" sheetId="28" r:id="Ra3575086f3f040a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0050" sheetId="29" r:id="R4670df45f3024323"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0051" sheetId="30" r:id="Rc1da6ea42c524765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0056" sheetId="31" r:id="R6ad7f61567c148ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0057" sheetId="32" r:id="R4b9cda8e93054d36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0058" sheetId="33" r:id="R0420e9be799d47cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0059" sheetId="34" r:id="R3e278cfae7a042aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0060" sheetId="35" r:id="Reb7caab5597a4f3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0061" sheetId="36" r:id="R7edbd335675a45b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0062" sheetId="37" r:id="R3e356f2078b241c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0052" sheetId="38" r:id="Rbac6803c2b88410f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0053" sheetId="39" r:id="R3c35d461d7d74cf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0054" sheetId="40" r:id="Rda88acefb5f94226"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0055" sheetId="41" r:id="R5592511802ca4cfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0063" sheetId="42" r:id="R492d1f6e31dd43f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0064" sheetId="43" r:id="R5c4d6161b6144984"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0065" sheetId="44" r:id="Rb3e64b37b1084c47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0066" sheetId="45" r:id="R080b50ecb96c41b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0067" sheetId="46" r:id="R6f46440e87d64d8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0068" sheetId="47" r:id="Rff00009dc44c46d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0069" sheetId="48" r:id="R09bc2556774c4214"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0070" sheetId="49" r:id="R6692e56c155b4e58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0071" sheetId="50" r:id="Rbb2634d9a09943a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0072" sheetId="51" r:id="Rd3c89f2d133946ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0073" sheetId="52" r:id="R61552ff57162430b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0074" sheetId="53" r:id="Raa518e5afd4640c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0075" sheetId="54" r:id="R01cc85f0bc294b7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0076" sheetId="55" r:id="Rcf289c2b5bfa4dd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0077" sheetId="56" r:id="R492d046c49ff4b2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0078" sheetId="57" r:id="Rb1c07f08436748a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0079" sheetId="58" r:id="Ra58d91f3325848de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0080" sheetId="59" r:id="R21c1777f5f8748aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0081" sheetId="60" r:id="Ree9a9aa3a1b245e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0082" sheetId="61" r:id="R923db5196ff44322"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0083" sheetId="62" r:id="R31778917826a445f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0084" sheetId="63" r:id="Ra5082b1570b14e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0085" sheetId="64" r:id="Rfebd417cc7af40e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Directory" sheetId="65" r:id="R2d50f68a8b2f4cb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0086" sheetId="66" r:id="R10626b934cae40ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0087" sheetId="67" r:id="R83182cd840554ed9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0088" sheetId="68" r:id="Rf316af4c3321426f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0089" sheetId="69" r:id="R48999dae52914ff6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0090" sheetId="70" r:id="R0d3d62130ccc4d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0091" sheetId="71" r:id="R8165b8fd62f8406d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0092" sheetId="72" r:id="R468a07b3264842a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0093" sheetId="73" r:id="R7e986da562b04bc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0094" sheetId="74" r:id="R24ebc299457548c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0095" sheetId="75" r:id="R07bd7dfaae904fe3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0096" sheetId="76" r:id="R177a41d05b324315"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0097" sheetId="77" r:id="Rd92529714d90444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0098" sheetId="78" r:id="Rce1279993961464c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0099" sheetId="79" r:id="Rb49927e1ddf14a8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0100" sheetId="80" r:id="Rf35d8ed7b03748d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0101" sheetId="81" r:id="R7cace818146d4349"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0102" sheetId="82" r:id="Rc06cd615a30542ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0103" sheetId="83" r:id="R6a8918eae59f4ccf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0104" sheetId="84" r:id="Rf7b9d377c55f4241"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0105" sheetId="85" r:id="Re821162cba0a4cb1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -93,8 +97,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:fonts count="2">
     <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:sz val="11"/>
       <x:color theme="1"/>
       <x:name val="Calibri"/>
@@ -122,8 +134,9 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -500,7 +513,7 @@
         <x:v>Total COA Records</x:v>
       </x:c>
       <x:c r="B3" t="n">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3" t="str">
         <x:v>Synced from COA Database</x:v>
@@ -526,7 +539,7 @@
         <x:v>Average Purity %</x:v>
       </x:c>
       <x:c r="B5" t="n">
-        <x:v>99.595</x:v>
+        <x:v>99.6</x:v>
       </x:c>
       <x:c r="C5" t="str">
         <x:v>Populated purity results</x:v>
@@ -539,7 +552,7 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="B6" t="n">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C6"/>
       <x:c r="D6"/>
@@ -585,7 +598,7 @@
         <x:v>Latest COA Date</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>2026-10-27</x:v>
       </x:c>
       <x:c r="C10"/>
       <x:c r="D10"/>
@@ -1104,7 +1117,7 @@
         <x:v>Total COA/Test Records</x:v>
       </x:c>
       <x:c r="B3" t="n">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3" t="str">
         <x:v>All records from COA Database</x:v>
@@ -1185,7 +1198,7 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="B6" t="n">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C6" t="str">
         <x:v>Status column</x:v>
@@ -1266,7 +1279,7 @@
         <x:v>Average Purity %</x:v>
       </x:c>
       <x:c r="B9" t="n">
-        <x:v>99.595</x:v>
+        <x:v>99.6</x:v>
       </x:c>
       <x:c r="C9" t="str">
         <x:v>Based on populated purity values</x:v>
@@ -1320,7 +1333,7 @@
         <x:v>Last Test Date</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>2026-10-27</x:v>
       </x:c>
       <x:c r="C11" t="str">
         <x:v>Most recent test date</x:v>
@@ -7355,6 +7368,242 @@
         <x:v>Reported 2026-10-14. BPC-157 acetate; HPLC VWD SOP-043: potency 24.36%, 243.62mg/g, 19.66mg/unit. Expanded uncertainty +/-7.81% at 95% confidence. No sterility or endotoxin results supplied.</x:v>
       </x:c>
     </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D115" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E115" t="n">
+        <x:v>113.38</x:v>
+      </x:c>
+      <x:c r="F115" t="n">
+        <x:v>13.38</x:v>
+      </x:c>
+      <x:c r="G115" t="n">
+        <x:v>0.1338</x:v>
+      </x:c>
+      <x:c r="H115" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I115" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J115" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K115" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="L115" t="str">
+        <x:v>2610190479</x:v>
+      </x:c>
+      <x:c r="M115" t="str">
+        <x:v>RTPe2610190479</x:v>
+      </x:c>
+      <x:c r="N115" t="str">
+        <x:v>Light Blue Cap</x:v>
+      </x:c>
+      <x:c r="O115" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="P115" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="Q115" t="str">
+        <x:v>Light Blue</x:v>
+      </x:c>
+      <x:c r="R115" t="str">
+        <x:v>Cap: Light Blue; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="S115" t="str">
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>Cellular Support</x:v>
+      </x:c>
+      <x:c r="D116" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E116" t="n">
+        <x:v>1054.63</x:v>
+      </x:c>
+      <x:c r="F116" t="n">
+        <x:v>54.63</x:v>
+      </x:c>
+      <x:c r="G116" t="n">
+        <x:v>0.054630000000000005</x:v>
+      </x:c>
+      <x:c r="H116" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I116" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J116" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K116" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="L116" t="str">
+        <x:v>2610190475</x:v>
+      </x:c>
+      <x:c r="M116" t="str">
+        <x:v>RTPe2610190475</x:v>
+      </x:c>
+      <x:c r="N116" t="str">
+        <x:v>White Cap</x:v>
+      </x:c>
+      <x:c r="O116" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="P116" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="Q116" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="R116" t="str">
+        <x:v>Cap: White; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="S116" t="str">
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D117" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E117" t="n">
+        <x:v>10.94</x:v>
+      </x:c>
+      <x:c r="F117" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="G117" t="n">
+        <x:v>0.094</x:v>
+      </x:c>
+      <x:c r="H117" t="n">
+        <x:v>99.3905</x:v>
+      </x:c>
+      <x:c r="I117" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J117" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K117" t="str">
+        <x:v>2026-10-27</x:v>
+      </x:c>
+      <x:c r="L117" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="M117" t="str">
+        <x:v>BYFJEIELXUE7</x:v>
+      </x:c>
+      <x:c r="N117" t="str">
+        <x:v>RE10-2610RT</x:v>
+      </x:c>
+      <x:c r="O117" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="P117" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="Q117" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="R117" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="S117" t="str">
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D118" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E118" t="n">
+        <x:v>12.76</x:v>
+      </x:c>
+      <x:c r="F118" t="n">
+        <x:v>2.76</x:v>
+      </x:c>
+      <x:c r="G118" t="n">
+        <x:v>0.27599999999999997</x:v>
+      </x:c>
+      <x:c r="H118" t="n">
+        <x:v>99.51</x:v>
+      </x:c>
+      <x:c r="I118" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J118" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K118" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="L118" t="str">
+        <x:v>RT10-20260918S2146</x:v>
+      </x:c>
+      <x:c r="M118" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="N118" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="O118" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="P118" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="Q118" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="R118" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="S118" t="str">
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -18807,6 +19056,278 @@
         <x:v>Purple cap / silver crimp visible or listed in supplied report.</x:v>
       </x:c>
     </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D103" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E103" t="n">
+        <x:v>113.38</x:v>
+      </x:c>
+      <x:c r="F103" t="n">
+        <x:v>13.38</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>0.1338</x:v>
+      </x:c>
+      <x:c r="H103" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L103" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="M103" t="str">
+        <x:v>2610190479</x:v>
+      </x:c>
+      <x:c r="N103" t="str">
+        <x:v>RTPe2610190479</x:v>
+      </x:c>
+      <x:c r="O103" t="str">
+        <x:v>Light Blue Cap</x:v>
+      </x:c>
+      <x:c r="P103" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="Q103" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R103" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S103" t="str">
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+      <x:c r="T103" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U103" t="str">
+        <x:v>Light Blue</x:v>
+      </x:c>
+      <x:c r="V103" t="str">
+        <x:v>Cap: Light Blue; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Cellular Support</x:v>
+      </x:c>
+      <x:c r="D104" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E104" t="n">
+        <x:v>1054.63</x:v>
+      </x:c>
+      <x:c r="F104" t="n">
+        <x:v>54.63</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>0.054630000000000005</x:v>
+      </x:c>
+      <x:c r="H104" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K104" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L104" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="M104" t="str">
+        <x:v>2610190475</x:v>
+      </x:c>
+      <x:c r="N104" t="str">
+        <x:v>RTPe2610190475</x:v>
+      </x:c>
+      <x:c r="O104" t="str">
+        <x:v>White Cap</x:v>
+      </x:c>
+      <x:c r="P104" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/nad-plus/NAD-1000mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="Q104" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R104" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S104" t="str">
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+      <x:c r="T104" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U104" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="V104" t="str">
+        <x:v>Cap: White; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D105" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E105" t="n">
+        <x:v>10.94</x:v>
+      </x:c>
+      <x:c r="F105" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="G105" t="n">
+        <x:v>0.094</x:v>
+      </x:c>
+      <x:c r="H105" t="n">
+        <x:v>99.3905</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J105" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K105" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L105" t="str">
+        <x:v>2026-10-27</x:v>
+      </x:c>
+      <x:c r="M105" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N105" t="str">
+        <x:v>BYFJEIELXUE7</x:v>
+      </x:c>
+      <x:c r="O105" t="str">
+        <x:v>RE10-2610RT</x:v>
+      </x:c>
+      <x:c r="P105" t="str">
+        <x:v>assets/coa/images/janoshik/retatrutide/Retatrutide-10mg-2026-10-27.jpg</x:v>
+      </x:c>
+      <x:c r="Q105" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R105" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S105" t="str">
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
+      </x:c>
+      <x:c r="T105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="V105" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D106" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E106" t="n">
+        <x:v>12.76</x:v>
+      </x:c>
+      <x:c r="F106" t="n">
+        <x:v>2.76</x:v>
+      </x:c>
+      <x:c r="G106" t="n">
+        <x:v>0.27599999999999997</x:v>
+      </x:c>
+      <x:c r="H106" t="n">
+        <x:v>99.51</x:v>
+      </x:c>
+      <x:c r="I106" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J106" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K106" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L106" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="M106" t="str">
+        <x:v>RT10-20260918S2146</x:v>
+      </x:c>
+      <x:c r="N106" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="O106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="P106" t="str">
+        <x:v>assets/coa/documents/tianjin-qiangxin/retatrutide/RT10-20260918S2146_report.pdf</x:v>
+      </x:c>
+      <x:c r="Q106" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R106" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S106" t="str">
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
+      </x:c>
+      <x:c r="T106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="V106" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -20539,43 +21060,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>COA-0005</x:v>
+        <x:v>COA-0102</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Cosmetic / Recovery</x:v>
       </x:c>
       <x:c r="E4" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F4" t="n">
-        <x:v>11.77</x:v>
+        <x:v>113.38</x:v>
       </x:c>
       <x:c r="G4" t="n">
-        <x:v>0.177</x:v>
+        <x:v>0.1338</x:v>
       </x:c>
       <x:c r="H4" t="n">
-        <x:v>99.963</x:v>
+        <x:v>99.99</x:v>
       </x:c>
       <x:c r="I4" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K4" t="n">
-        <x:v>46117</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K4" t="str">
+        <x:v>2026-10-20</x:v>
       </x:c>
       <x:c r="L4" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Light Blue</x:v>
       </x:c>
       <x:c r="M4" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Not listed</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>Trivial-3R / Retatrutide; batch avg</x:v>
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -20583,43 +21104,43 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>COA-0019</x:v>
+        <x:v>COA-0103</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Cellular Support</x:v>
       </x:c>
       <x:c r="E5" t="n">
-        <x:v>10</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="F5" t="n">
-        <x:v>8.88</x:v>
+        <x:v>1054.63</x:v>
       </x:c>
       <x:c r="G5" t="n">
-        <x:v>-0.1119999999999999</x:v>
+        <x:v>0.054630000000000005</x:v>
       </x:c>
       <x:c r="H5" t="n">
-        <x:v>99.95</x:v>
+        <x:v>99.99</x:v>
       </x:c>
       <x:c r="I5" t="str">
-        <x:v>Underfilled</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K5" t="n">
-        <x:v>46155</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>2026-10-20</x:v>
       </x:c>
       <x:c r="L5" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>White</x:v>
       </x:c>
       <x:c r="M5" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Not listed</x:v>
       </x:c>
       <x:c r="N5" t="str">
-        <x:v>Elamipretide; tested twice</x:v>
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -20627,34 +21148,34 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>COA-0063</x:v>
+        <x:v>COA-0005</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>5-Amino-1MQ</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D6" t="str">
-        <x:v>Metabolic / Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E6" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F6" t="n">
-        <x:v>5.27</x:v>
+        <x:v>11.77</x:v>
       </x:c>
       <x:c r="G6" t="n">
-        <x:v>0.053999999999999916</x:v>
+        <x:v>0.177</x:v>
       </x:c>
       <x:c r="H6" t="n">
-        <x:v>99.93</x:v>
+        <x:v>99.963</x:v>
       </x:c>
       <x:c r="I6" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J6" t="str">
-        <x:v>ILS Labs</x:v>
-      </x:c>
-      <x:c r="K6" t="str">
-        <x:v>08/29/2026</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K6" t="n">
+        <x:v>46117</x:v>
       </x:c>
       <x:c r="L6" t="str">
         <x:v>Not Listed</x:v>
@@ -20663,7 +21184,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N6" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.93%; net content 5.27 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code GJA8JYCE.</x:v>
+        <x:v>Trivial-3R / Retatrutide; batch avg</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -20671,43 +21192,43 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>COA-0027</x:v>
+        <x:v>COA-0019</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>ADAMAX</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="D7" t="str">
-        <x:v>Research Peptide</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F7" t="n">
-        <x:v>10.92</x:v>
+        <x:v>8.88</x:v>
       </x:c>
       <x:c r="G7" t="n">
-        <x:v>0.092</x:v>
+        <x:v>-0.1119999999999999</x:v>
       </x:c>
       <x:c r="H7" t="n">
-        <x:v>99.91</x:v>
+        <x:v>99.95</x:v>
       </x:c>
       <x:c r="I7" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="J7" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K7" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K7" t="n">
+        <x:v>46155</x:v>
       </x:c>
       <x:c r="L7" t="str">
-        <x:v>Clear</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M7" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N7" t="str">
-        <x:v>Adamax 10mg with heavy metal and endotoxin screen</x:v>
+        <x:v>Elamipretide; tested twice</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -20715,43 +21236,43 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>COA-0055</x:v>
+        <x:v>COA-0063</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>5-Amino-1MQ</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Metabolic / Research</x:v>
       </x:c>
       <x:c r="E8" t="n">
-        <x:v>40</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" t="n">
-        <x:v>43.16</x:v>
+        <x:v>5.27</x:v>
       </x:c>
       <x:c r="G8" t="n">
-        <x:v>0.079</x:v>
+        <x:v>0.053999999999999916</x:v>
       </x:c>
       <x:c r="H8" t="n">
-        <x:v>99.9</x:v>
+        <x:v>99.93</x:v>
       </x:c>
       <x:c r="I8" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>08/29/2026</x:v>
       </x:c>
       <x:c r="L8" t="str">
-        <x:v>Clear Purple</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M8" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 43.16 mg. Client: Tomcat Peptides. Accession 2608250164; received 08/25/2026; reported 08/29/2026.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.93%; net content 5.27 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code GJA8JYCE.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -20759,43 +21280,43 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>COA-0085</x:v>
+        <x:v>COA-0027</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>ADAMAX</x:v>
       </x:c>
       <x:c r="D9" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>Research Peptide</x:v>
       </x:c>
       <x:c r="E9" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F9" t="n">
-        <x:v>41.14</x:v>
+        <x:v>10.92</x:v>
       </x:c>
       <x:c r="G9" t="n">
-        <x:v>0.028500000000000015</x:v>
+        <x:v>0.092</x:v>
       </x:c>
       <x:c r="H9" t="n">
-        <x:v>99.9</x:v>
+        <x:v>99.91</x:v>
       </x:c>
       <x:c r="I9" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K9" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="L9" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="M9" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N9" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.9%; net content 41.14 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code UYWCCYSG.</x:v>
+        <x:v>Adamax 10mg with heavy metal and endotoxin screen</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -20803,22 +21324,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>COA-0097</x:v>
+        <x:v>COA-0085</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D10" t="str">
-        <x:v>Metabolic / Mitochondrial</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E10" t="n">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F10" t="n">
-        <x:v>9.5</x:v>
+        <x:v>41.14</x:v>
       </x:c>
       <x:c r="G10" t="n">
-        <x:v>-0.05</x:v>
+        <x:v>0.028500000000000015</x:v>
       </x:c>
       <x:c r="H10" t="n">
         <x:v>99.9</x:v>
@@ -20827,19 +21348,19 @@
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>BTLabs</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L10" t="str">
-        <x:v>Green</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M10" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>Issued 2026-08-26. HPLC potency 9.5mg (94.6% as printed). Gross powder mass 124.2mg includes excipients and is NOT peptide content. FTIR confirms composition. No microbial/endotoxin testing provided.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.9%; net content 41.14 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code UYWCCYSG.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -20847,43 +21368,43 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>COA-0021</x:v>
+        <x:v>COA-0055</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>CJC-1295 No DAC</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D11" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E11" t="n">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F11" t="n">
-        <x:v>9.66</x:v>
+        <x:v>43.16</x:v>
       </x:c>
       <x:c r="G11" t="n">
-        <x:v>-0.03399999999999999</x:v>
+        <x:v>0.079</x:v>
       </x:c>
       <x:c r="H11" t="n">
-        <x:v>99.897</x:v>
+        <x:v>99.9</x:v>
       </x:c>
       <x:c r="I11" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K11" t="n">
-        <x:v>46156</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="L11" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Clear Purple</x:v>
       </x:c>
       <x:c r="M11" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>Mod GRF 1-29</x:v>
+        <x:v>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 43.16 mg. Client: Tomcat Peptides. Accession 2608250164; received 08/25/2026; reported 08/29/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -20891,43 +21412,43 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>COA-0012</x:v>
+        <x:v>COA-0097</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>AOD-9604</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D12" t="str">
-        <x:v>Metabolic / Fat Loss</x:v>
+        <x:v>Metabolic / Mitochondrial</x:v>
       </x:c>
       <x:c r="E12" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F12" t="n">
-        <x:v>5.95</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="G12" t="n">
-        <x:v>0.19</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="H12" t="n">
-        <x:v>99.883</x:v>
+        <x:v>99.9</x:v>
       </x:c>
       <x:c r="I12" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K12" t="n">
-        <x:v>46156</x:v>
+        <x:v>BTLabs</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="L12" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Green</x:v>
       </x:c>
       <x:c r="M12" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N12" t="str">
-        <x:v>rHGH fragment / AOD-9604</x:v>
+        <x:v>Issued 2026-08-26. HPLC potency 9.5mg (94.6% as printed). Gross powder mass 124.2mg includes excipients and is NOT peptide content. FTIR confirms composition. No microbial/endotoxin testing provided.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -20935,43 +21456,43 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>COA-0024</x:v>
+        <x:v>COA-0021</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>CJC-1295 No DAC</x:v>
       </x:c>
       <x:c r="D13" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E13" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F13" t="n">
-        <x:v>22.47</x:v>
+        <x:v>9.66</x:v>
       </x:c>
       <x:c r="G13" t="n">
-        <x:v>0.1234999999999999</x:v>
+        <x:v>-0.03399999999999999</x:v>
       </x:c>
       <x:c r="H13" t="n">
-        <x:v>99.86</x:v>
+        <x:v>99.897</x:v>
       </x:c>
       <x:c r="I13" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>Freedom Diagnostics</x:v>
-      </x:c>
-      <x:c r="K13" t="str">
-        <x:v>2026-06-14</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K13" t="n">
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L13" t="str">
-        <x:v>Clear Green</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M13" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>Retatrutide 20mg, separate batch from existing Retatrutide records; received 06/11/2026, reported 06/14/2026.</x:v>
+        <x:v>Mod GRF 1-29</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -20979,34 +21500,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>COA-0057</x:v>
+        <x:v>COA-0012</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>AOD-9604</x:v>
       </x:c>
       <x:c r="D14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Metabolic / Fat Loss</x:v>
       </x:c>
       <x:c r="E14" t="n">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F14" t="n">
-        <x:v>37.37</x:v>
+        <x:v>5.95</x:v>
       </x:c>
       <x:c r="G14" t="n">
-        <x:v>0.24566666666666667</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="H14" t="n">
-        <x:v>99.86</x:v>
+        <x:v>99.883</x:v>
       </x:c>
       <x:c r="I14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>Pristin Biotech</x:v>
-      </x:c>
-      <x:c r="K14" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K14" t="n">
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L14" t="str">
         <x:v>Not Listed</x:v>
@@ -21015,7 +21536,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>Identity detected by LCMS/MS; HPLC purity 99.86%; net peptide content 37.37 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</x:v>
+        <x:v>rHGH fragment / AOD-9604</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -21023,34 +21544,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>COA-0069</x:v>
+        <x:v>COA-0057</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>GHK-Cu</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D15" t="str">
-        <x:v>Cosmetic / Skin Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E15" t="n">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F15" t="n">
-        <x:v>52.21</x:v>
+        <x:v>37.37</x:v>
       </x:c>
       <x:c r="G15" t="n">
-        <x:v>0.04420000000000002</x:v>
+        <x:v>0.24566666666666667</x:v>
       </x:c>
       <x:c r="H15" t="n">
-        <x:v>99.85</x:v>
+        <x:v>99.86</x:v>
       </x:c>
       <x:c r="I15" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J15" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Pristin Biotech</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="L15" t="str">
         <x:v>Not Listed</x:v>
@@ -21059,7 +21580,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.85%; net content 52.21 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 3SDBWEB6.</x:v>
+        <x:v>Identity detected by LCMS/MS; HPLC purity 99.86%; net peptide content 37.37 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -21067,43 +21588,43 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>COA-0093</x:v>
+        <x:v>COA-0024</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D16" t="str">
-        <x:v>Amylin / Weight</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E16" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F16" t="n">
-        <x:v>10.14</x:v>
+        <x:v>22.47</x:v>
       </x:c>
       <x:c r="G16" t="n">
-        <x:v>0.014000000000000002</x:v>
+        <x:v>0.1234999999999999</x:v>
       </x:c>
       <x:c r="H16" t="n">
-        <x:v>99.85</x:v>
+        <x:v>99.86</x:v>
       </x:c>
       <x:c r="I16" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>PurePoint Analytical</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>2026-10-01</x:v>
+        <x:v>2026-06-14</x:v>
       </x:c>
       <x:c r="L16" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Clear Green</x:v>
       </x:c>
       <x:c r="M16" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>Issued 2026-10-02. Identity confirmed by LC-MS; HPLC/UV purity and net content passed.</x:v>
+        <x:v>Retatrutide 20mg, separate batch from existing Retatrutide records; received 06/11/2026, reported 06/14/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -21111,43 +21632,43 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>COA-0050</x:v>
+        <x:v>COA-0069</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D17" t="str">
-        <x:v>Amylin / Weight</x:v>
+        <x:v>Cosmetic / Skin Research</x:v>
       </x:c>
       <x:c r="E17" t="n">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F17" t="n">
-        <x:v>10.38</x:v>
+        <x:v>52.21</x:v>
       </x:c>
       <x:c r="G17" t="n">
-        <x:v>0.038</x:v>
+        <x:v>0.04420000000000002</x:v>
       </x:c>
       <x:c r="H17" t="n">
-        <x:v>99.849</x:v>
+        <x:v>99.85</x:v>
       </x:c>
       <x:c r="I17" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J17" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K17" t="n">
-        <x:v>46242</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K17" t="str">
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L17" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M17" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>Identity confirmed as Cagrilintide by LC-MS. Endotoxin PASS; microbial sterility: No Growth. Vial 1: 99.827% / 10.29 mg; vial 2: 99.871% / 10.46 mg. Certified 08/08/2026.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.85%; net content 52.21 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 3SDBWEB6.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -21155,43 +21676,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>COA-0013</x:v>
+        <x:v>COA-0093</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Cagrilintide</x:v>
       </x:c>
       <x:c r="D18" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Amylin / Weight</x:v>
       </x:c>
       <x:c r="E18" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F18" t="n">
-        <x:v>10.58</x:v>
+        <x:v>10.14</x:v>
       </x:c>
       <x:c r="G18" t="n">
-        <x:v>0.05800000000000001</x:v>
+        <x:v>0.014000000000000002</x:v>
       </x:c>
       <x:c r="H18" t="n">
-        <x:v>99.847</x:v>
+        <x:v>99.85</x:v>
       </x:c>
       <x:c r="I18" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J18" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K18" t="n">
-        <x:v>46057</x:v>
+        <x:v>PurePoint Analytical</x:v>
+      </x:c>
+      <x:c r="K18" t="str">
+        <x:v>2026-10-01</x:v>
       </x:c>
       <x:c r="L18" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M18" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>10 mg label</x:v>
+        <x:v>Issued 2026-10-02. Identity confirmed by LC-MS; HPLC/UV purity and net content passed.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -21199,43 +21720,43 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>COA-0010</x:v>
+        <x:v>COA-0050</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Cagrilintide</x:v>
       </x:c>
       <x:c r="D19" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Amylin / Weight</x:v>
       </x:c>
       <x:c r="E19" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F19" t="n">
-        <x:v>32.5</x:v>
+        <x:v>10.38</x:v>
       </x:c>
       <x:c r="G19" t="n">
-        <x:v>0.08333333333333333</x:v>
+        <x:v>0.038</x:v>
       </x:c>
       <x:c r="H19" t="n">
-        <x:v>99.84</x:v>
+        <x:v>99.849</x:v>
       </x:c>
       <x:c r="I19" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J19" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K19" t="n">
-        <x:v>46059</x:v>
+        <x:v>46242</x:v>
       </x:c>
       <x:c r="L19" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M19" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>30 mg label</x:v>
+        <x:v>Identity confirmed as Cagrilintide by LC-MS. Endotoxin PASS; microbial sterility: No Growth. Vial 1: 99.827% / 10.29 mg; vial 2: 99.871% / 10.46 mg. Certified 08/08/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -21243,34 +21764,34 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>COA-0070</x:v>
+        <x:v>COA-0013</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>GLOW</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D20" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E20" t="n">
-        <x:v>70</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F20" t="n">
-        <x:v>72.68</x:v>
+        <x:v>10.58</x:v>
       </x:c>
       <x:c r="G20" t="n">
-        <x:v>0.03828571428571438</x:v>
+        <x:v>0.05800000000000001</x:v>
       </x:c>
       <x:c r="H20" t="n">
-        <x:v>99.84</x:v>
+        <x:v>99.847</x:v>
       </x:c>
       <x:c r="I20" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>ILS Labs</x:v>
-      </x:c>
-      <x:c r="K20" t="str">
-        <x:v>08/28/2026</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K20" t="n">
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L20" t="str">
         <x:v>Not Listed</x:v>
@@ -21279,7 +21800,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.84%; net content 72.68 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code CAB37LKM.</x:v>
+        <x:v>10 mg label</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -21287,34 +21808,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>COA-0058</x:v>
+        <x:v>COA-0070</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>GLOW</x:v>
       </x:c>
       <x:c r="D21" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
       <x:c r="E21" t="n">
-        <x:v>10</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F21" t="n">
-        <x:v>10.8</x:v>
+        <x:v>72.68</x:v>
       </x:c>
       <x:c r="G21" t="n">
-        <x:v>0.08</x:v>
+        <x:v>0.03828571428571438</x:v>
       </x:c>
       <x:c r="H21" t="n">
-        <x:v>99.83</x:v>
+        <x:v>99.84</x:v>
       </x:c>
       <x:c r="I21" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>Pristin Biotech</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>08/28/2026</x:v>
       </x:c>
       <x:c r="L21" t="str">
         <x:v>Not Listed</x:v>
@@ -21323,7 +21844,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>Identity detected by LCMS/MS; HPLC purity 99.83%; net peptide content 10.80 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.84%; net content 72.68 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code CAB37LKM.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -21331,10 +21852,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>COA-0022</x:v>
+        <x:v>COA-0010</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D22" t="str">
         <x:v>GLP-1 / Weight</x:v>
@@ -21343,13 +21864,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="F22" t="n">
-        <x:v>34.77</x:v>
+        <x:v>32.5</x:v>
       </x:c>
       <x:c r="G22" t="n">
-        <x:v>0.1590000000000001</x:v>
+        <x:v>0.08333333333333333</x:v>
       </x:c>
       <x:c r="H22" t="n">
-        <x:v>99.825</x:v>
+        <x:v>99.84</x:v>
       </x:c>
       <x:c r="I22" t="str">
         <x:v>Overfilled</x:v>
@@ -21358,7 +21879,7 @@
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K22" t="n">
-        <x:v>46156</x:v>
+        <x:v>46059</x:v>
       </x:c>
       <x:c r="L22" t="str">
         <x:v>Not Listed</x:v>
@@ -21367,7 +21888,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>RT30 Retatrutide 30mg; common GLP-1 blind test; overfilled.</x:v>
+        <x:v>30 mg label</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -21375,43 +21896,43 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>COA-0036</x:v>
+        <x:v>COA-0058</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>KLOW 80mg</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D23" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E23" t="n">
-        <x:v>80</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F23" t="n">
-        <x:v>96.46</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="G23" t="n">
-        <x:v>0.20575000000000002</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="H23" t="n">
-        <x:v>99.82</x:v>
+        <x:v>99.83</x:v>
       </x:c>
       <x:c r="I23" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J23" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>Pristin Biotech</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="L23" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M23" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>Identity confirmed: GHK-Cu/KPV/BPC-157/Thymosin Beta-4. Net content: GHK-Cu 62.93 mg; KPV 9.09 mg; BPC-157 12.40 mg; Thymosin Beta-4 12.04 mg. Blue lyophilized powder. Received 07/17/2026; reported 07/20/2026.</x:v>
+        <x:v>Identity detected by LCMS/MS; HPLC purity 99.83%; net peptide content 10.80 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -21419,43 +21940,43 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>COA-0090</x:v>
+        <x:v>COA-0022</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D24" t="str">
-        <x:v>Metabolic / Mitochondrial Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E24" t="n">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F24" t="n">
-        <x:v>58.95</x:v>
+        <x:v>34.77</x:v>
       </x:c>
       <x:c r="G24" t="n">
-        <x:v>0.179</x:v>
+        <x:v>0.1590000000000001</x:v>
       </x:c>
       <x:c r="H24" t="n">
-        <x:v>99.82</x:v>
+        <x:v>99.825</x:v>
       </x:c>
       <x:c r="I24" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>Freedom Diagnostics</x:v>
-      </x:c>
-      <x:c r="K24" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K24" t="n">
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L24" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M24" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.82%; net content 58.95 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.84% / 59.02 mg and 99.79% / 58.88 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>RT30 Retatrutide 30mg; common GLP-1 blind test; overfilled.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -21463,43 +21984,43 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>COA-0015</x:v>
+        <x:v>COA-0090</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="D25" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Metabolic / Mitochondrial Research</x:v>
       </x:c>
       <x:c r="E25" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F25" t="n">
-        <x:v>38.96</x:v>
+        <x:v>58.95</x:v>
       </x:c>
       <x:c r="G25" t="n">
-        <x:v>-0.02599999999999998</x:v>
+        <x:v>0.179</x:v>
       </x:c>
       <x:c r="H25" t="n">
-        <x:v>99.813</x:v>
+        <x:v>99.82</x:v>
       </x:c>
       <x:c r="I25" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K25" t="n">
-        <x:v>46057</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="L25" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M25" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>40 mg label</x:v>
+        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.82%; net content 58.95 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.84% / 59.02 mg and 99.79% / 58.88 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -21507,43 +22028,43 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>COA-0028</x:v>
+        <x:v>COA-0036</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>BPC/TB Blend</x:v>
+        <x:v>KLOW 80mg</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
       <x:c r="E26" t="n">
-        <x:v>10</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F26" t="n">
-        <x:v>11.85</x:v>
+        <x:v>96.46</x:v>
       </x:c>
       <x:c r="G26" t="n">
-        <x:v>0.185</x:v>
+        <x:v>0.20575000000000002</x:v>
       </x:c>
       <x:c r="H26" t="n">
-        <x:v>99.81</x:v>
+        <x:v>99.82</x:v>
       </x:c>
       <x:c r="I26" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="L26" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M26" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N26" t="str">
-        <x:v>BPC-157 5.76mg + TB-500 6.09mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Identity confirmed: GHK-Cu/KPV/BPC-157/Thymosin Beta-4. Net content: GHK-Cu 62.93 mg; KPV 9.09 mg; BPC-157 12.40 mg; Thymosin Beta-4 12.04 mg. Blue lyophilized powder. Received 07/17/2026; reported 07/20/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -21551,43 +22072,43 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>COA-0009</x:v>
+        <x:v>COA-0015</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E27" t="n">
-        <x:v>60</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F27" t="n">
-        <x:v>65.1</x:v>
+        <x:v>38.96</x:v>
       </x:c>
       <x:c r="G27" t="n">
-        <x:v>0.08499999999999991</x:v>
+        <x:v>-0.02599999999999998</x:v>
       </x:c>
       <x:c r="H27" t="n">
-        <x:v>99.8</x:v>
+        <x:v>99.813</x:v>
       </x:c>
       <x:c r="I27" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J27" t="str">
-        <x:v>BT Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K27" t="n">
-        <x:v>46133</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L27" t="str">
-        <x:v>Gold</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M27" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>60 mg label; 108.5% potency</x:v>
+        <x:v>40 mg label</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -21595,34 +22116,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>COA-0056</x:v>
+        <x:v>COA-0028</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>Tesamorelin</x:v>
+        <x:v>BPC/TB Blend</x:v>
       </x:c>
       <x:c r="D28" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E28" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F28" t="n">
-        <x:v>12.18</x:v>
+        <x:v>11.85</x:v>
       </x:c>
       <x:c r="G28" t="n">
-        <x:v>0.21800000000000003</x:v>
+        <x:v>0.185</x:v>
       </x:c>
       <x:c r="H28" t="n">
-        <x:v>99.79</x:v>
+        <x:v>99.81</x:v>
       </x:c>
       <x:c r="I28" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J28" t="str">
-        <x:v>Pristin Biotech</x:v>
+        <x:v>Testides</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L28" t="str">
         <x:v>Not Listed</x:v>
@@ -21631,7 +22152,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>Identity detected by LCMS/MS; HPLC purity 99.79%; net peptide content 12.18 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</x:v>
+        <x:v>BPC-157 5.76mg + TB-500 6.09mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -21639,43 +22160,43 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>COA-0071</x:v>
+        <x:v>COA-0009</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>KLOW</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D29" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E29" t="n">
-        <x:v>80</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F29" t="n">
-        <x:v>82.72</x:v>
+        <x:v>65.1</x:v>
       </x:c>
       <x:c r="G29" t="n">
-        <x:v>0.03399999999999999</x:v>
+        <x:v>0.08499999999999991</x:v>
       </x:c>
       <x:c r="H29" t="n">
-        <x:v>99.79</x:v>
+        <x:v>99.8</x:v>
       </x:c>
       <x:c r="I29" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J29" t="str">
-        <x:v>ILS Labs</x:v>
-      </x:c>
-      <x:c r="K29" t="str">
-        <x:v>08/28/2026</x:v>
+        <x:v>BT Labs</x:v>
+      </x:c>
+      <x:c r="K29" t="n">
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="L29" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Gold</x:v>
       </x:c>
       <x:c r="M29" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.79%; net content 82.72 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code GRD4V5KA.</x:v>
+        <x:v>60 mg label; 108.5% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -21683,22 +22204,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>COA-0078</x:v>
+        <x:v>COA-0087</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>KPV</x:v>
       </x:c>
       <x:c r="D30" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>Healing / Anti-Inflammatory Research</x:v>
       </x:c>
       <x:c r="E30" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F30" t="n">
-        <x:v>21.38</x:v>
+        <x:v>13.04</x:v>
       </x:c>
       <x:c r="G30" t="n">
-        <x:v>0.06899999999999995</x:v>
+        <x:v>0.304</x:v>
       </x:c>
       <x:c r="H30" t="n">
         <x:v>99.79</x:v>
@@ -21707,19 +22228,19 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J30" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="L30" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M30" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.79%; net content 21.38 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6V3BNXVB.</x:v>
+        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.79%; net content 13.04 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.78% / 13.21 mg and 99.80% / 12.87 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -21727,22 +22248,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>COA-0087</x:v>
+        <x:v>COA-0078</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>KPV</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D31" t="str">
-        <x:v>Healing / Anti-Inflammatory Research</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E31" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F31" t="n">
-        <x:v>13.04</x:v>
+        <x:v>21.38</x:v>
       </x:c>
       <x:c r="G31" t="n">
-        <x:v>0.304</x:v>
+        <x:v>0.06899999999999995</x:v>
       </x:c>
       <x:c r="H31" t="n">
         <x:v>99.79</x:v>
@@ -21751,19 +22272,19 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J31" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L31" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M31" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N31" t="str">
-        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.79%; net content 13.04 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.78% / 13.21 mg and 99.80% / 12.87 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.79%; net content 21.38 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6V3BNXVB.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -21771,43 +22292,43 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>COA-0041</x:v>
+        <x:v>COA-0071</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>GHK-Cu</x:v>
+        <x:v>KLOW</x:v>
       </x:c>
       <x:c r="D32" t="str">
-        <x:v>Cosmetic / Recovery</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
       <x:c r="E32" t="n">
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F32" t="n">
-        <x:v>51.34</x:v>
+        <x:v>82.72</x:v>
       </x:c>
       <x:c r="G32" t="n">
-        <x:v>0.026800000000000067</x:v>
+        <x:v>0.03399999999999999</x:v>
       </x:c>
       <x:c r="H32" t="n">
-        <x:v>99.78</x:v>
+        <x:v>99.79</x:v>
       </x:c>
       <x:c r="I32" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J32" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K32" t="n">
-        <x:v>46239</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>08/28/2026</x:v>
       </x:c>
       <x:c r="L32" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M32" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N32" t="str">
-        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.79%; net content 82.72 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code GRD4V5KA.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -21815,34 +22336,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>COA-0068</x:v>
+        <x:v>COA-0056</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>CJC-1295 / Ipamorelin</x:v>
+        <x:v>Tesamorelin</x:v>
       </x:c>
       <x:c r="D33" t="str">
-        <x:v>Growth Hormone Support Blend</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E33" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F33" t="n">
-        <x:v>10.47</x:v>
+        <x:v>12.18</x:v>
       </x:c>
       <x:c r="G33" t="n">
-        <x:v>0.04700000000000006</x:v>
+        <x:v>0.21800000000000003</x:v>
       </x:c>
       <x:c r="H33" t="n">
-        <x:v>99.78</x:v>
+        <x:v>99.79</x:v>
       </x:c>
       <x:c r="I33" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J33" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Pristin Biotech</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="L33" t="str">
         <x:v>Not Listed</x:v>
@@ -21851,7 +22372,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N33" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.78%; net content 10.47 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code VRDU58EW.</x:v>
+        <x:v>Identity detected by LCMS/MS; HPLC purity 99.79%; net peptide content 12.18 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -21859,43 +22380,43 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>COA-0035</x:v>
+        <x:v>COA-0068</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>GHK-Cu</x:v>
+        <x:v>CJC-1295 / Ipamorelin</x:v>
       </x:c>
       <x:c r="D34" t="str">
-        <x:v>Regenerative / Skin</x:v>
+        <x:v>Growth Hormone Support Blend</x:v>
       </x:c>
       <x:c r="E34" t="n">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F34" t="n">
-        <x:v>50.75</x:v>
+        <x:v>10.47</x:v>
       </x:c>
       <x:c r="G34" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.04700000000000006</x:v>
       </x:c>
       <x:c r="H34" t="n">
-        <x:v>99.77</x:v>
+        <x:v>99.78</x:v>
       </x:c>
       <x:c r="I34" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J34" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L34" t="str">
-        <x:v>Clear/Transparent</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M34" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N34" t="str">
-        <x:v>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.78%; net content 10.47 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code VRDU58EW.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -21903,43 +22424,43 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>COA-0034</x:v>
+        <x:v>COA-0041</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D35" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Cosmetic / Recovery</x:v>
       </x:c>
       <x:c r="E35" t="n">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F35" t="n">
-        <x:v>15.59</x:v>
+        <x:v>51.34</x:v>
       </x:c>
       <x:c r="G35" t="n">
-        <x:v>0.03933333333333333</x:v>
+        <x:v>0.026800000000000067</x:v>
       </x:c>
       <x:c r="H35" t="n">
-        <x:v>99.747</x:v>
+        <x:v>99.78</x:v>
       </x:c>
       <x:c r="I35" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J35" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K35" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K35" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L35" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M35" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N35" t="str">
-        <x:v>Kovera image COA; purple cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -21947,43 +22468,43 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>COA-0088</x:v>
+        <x:v>COA-0035</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D36" t="str">
-        <x:v>Metabolic / Mitochondrial Research</x:v>
+        <x:v>Regenerative / Skin</x:v>
       </x:c>
       <x:c r="E36" t="n">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F36" t="n">
-        <x:v>22.84</x:v>
+        <x:v>50.75</x:v>
       </x:c>
       <x:c r="G36" t="n">
-        <x:v>0.142</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="H36" t="n">
-        <x:v>99.74</x:v>
+        <x:v>99.77</x:v>
       </x:c>
       <x:c r="I36" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J36" t="str">
         <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>2026-09-18</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="L36" t="str">
-        <x:v>Black</x:v>
+        <x:v>Clear/Transparent</x:v>
       </x:c>
       <x:c r="M36" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N36" t="str">
-        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.74%; net content 22.84 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.73% / 22.96 mg and 99.75% / 22.71 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -21991,43 +22512,43 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>COA-0089</x:v>
+        <x:v>COA-0034</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D37" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E37" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F37" t="n">
-        <x:v>11.76</x:v>
+        <x:v>15.59</x:v>
       </x:c>
       <x:c r="G37" t="n">
-        <x:v>0.176</x:v>
+        <x:v>0.03933333333333333</x:v>
       </x:c>
       <x:c r="H37" t="n">
-        <x:v>99.74</x:v>
+        <x:v>99.747</x:v>
       </x:c>
       <x:c r="I37" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J37" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>2026-09-18</x:v>
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L37" t="str">
-        <x:v>Clear</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M37" t="str">
-        <x:v>Copper</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>Identity confirmed as GLP-RT by LC-MS; HPLC-UV purity 99.74%; net content 11.76 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.75% / 11.49 mg and 99.72% / 12.03 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Kovera image COA; purple cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -22035,43 +22556,43 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>COA-0023</x:v>
+        <x:v>COA-0089</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D38" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E38" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F38" t="n">
-        <x:v>16.18</x:v>
+        <x:v>11.76</x:v>
       </x:c>
       <x:c r="G38" t="n">
-        <x:v>0.07866666666666665</x:v>
+        <x:v>0.176</x:v>
       </x:c>
       <x:c r="H38" t="n">
-        <x:v>99.731</x:v>
+        <x:v>99.74</x:v>
       </x:c>
       <x:c r="I38" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J38" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K38" t="n">
-        <x:v>46156</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>2026-09-18</x:v>
       </x:c>
       <x:c r="L38" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="M38" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Copper</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>T15 Tirzepatide 15mg; common GLP-1 blind test; overfilled.</x:v>
+        <x:v>Identity confirmed as GLP-RT by LC-MS; HPLC-UV purity 99.74%; net content 11.76 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.75% / 11.49 mg and 99.72% / 12.03 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -22079,43 +22600,43 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>COA-0092</x:v>
+        <x:v>COA-0088</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D39" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>Metabolic / Mitochondrial Research</x:v>
       </x:c>
       <x:c r="E39" t="n">
-        <x:v>60</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F39" t="n">
-        <x:v>63.89</x:v>
+        <x:v>22.84</x:v>
       </x:c>
       <x:c r="G39" t="n">
-        <x:v>0.06483333333333334</x:v>
+        <x:v>0.142</x:v>
       </x:c>
       <x:c r="H39" t="n">
-        <x:v>99.727</x:v>
+        <x:v>99.74</x:v>
       </x:c>
       <x:c r="I39" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J39" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-09-18</x:v>
       </x:c>
       <x:c r="L39" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M39" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>Identity confirmed as TRZ by LC-MS; batch average purity 99.727%; batch average net content 63.89 mg. Endotoxin safety screen PASS; arsenic, cadmium, lead, and mercury negative. Vials: 99.676% / 63.96 mg and 99.777% / 63.81 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.74%; net content 22.84 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.73% / 22.96 mg and 99.75% / 22.71 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -22123,34 +22644,34 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>COA-0045</x:v>
+        <x:v>COA-0023</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>CJC-1295</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D40" t="str">
-        <x:v>GHRH analog</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E40" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F40" t="n">
-        <x:v>10.52</x:v>
+        <x:v>16.18</x:v>
       </x:c>
       <x:c r="G40" t="n">
-        <x:v>0.051999999999999956</x:v>
+        <x:v>0.07866666666666665</x:v>
       </x:c>
       <x:c r="H40" t="n">
-        <x:v>99.72</x:v>
+        <x:v>99.731</x:v>
       </x:c>
       <x:c r="I40" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J40" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K40" t="n">
-        <x:v>46234</x:v>
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L40" t="str">
         <x:v>Not Listed</x:v>
@@ -22159,7 +22680,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
+        <x:v>T15 Tirzepatide 15mg; common GLP-1 blind test; overfilled.</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -22167,43 +22688,43 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>COA-0054</x:v>
+        <x:v>COA-0092</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D41" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E41" t="n">
-        <x:v>20</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F41" t="n">
-        <x:v>21.94</x:v>
+        <x:v>63.89</x:v>
       </x:c>
       <x:c r="G41" t="n">
-        <x:v>0.097</x:v>
+        <x:v>0.06483333333333334</x:v>
       </x:c>
       <x:c r="H41" t="n">
-        <x:v>99.72</x:v>
+        <x:v>99.727</x:v>
       </x:c>
       <x:c r="I41" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J41" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="L41" t="str">
-        <x:v>Clear Pink</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M41" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 21.94 mg. Client: Tomcat Peptides. Accession 2608250163; received 08/25/2026; reported 08/29/2026.</x:v>
+        <x:v>Identity confirmed as TRZ by LC-MS; batch average purity 99.727%; batch average net content 63.89 mg. Endotoxin safety screen PASS; arsenic, cadmium, lead, and mercury negative. Vials: 99.676% / 63.96 mg and 99.777% / 63.81 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -22255,43 +22776,43 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" t="str">
-        <x:v>COA-0075</x:v>
+        <x:v>COA-0054</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>Melanotan II</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D43" t="str">
-        <x:v>Pigmentation / Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E43" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F43" t="n">
-        <x:v>10.34</x:v>
+        <x:v>21.94</x:v>
       </x:c>
       <x:c r="G43" t="n">
-        <x:v>0.03399999999999999</x:v>
+        <x:v>0.097</x:v>
       </x:c>
       <x:c r="H43" t="n">
-        <x:v>99.71</x:v>
+        <x:v>99.72</x:v>
       </x:c>
       <x:c r="I43" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J43" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K43" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="L43" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Clear Pink</x:v>
       </x:c>
       <x:c r="M43" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N43" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.71%; net content 10.34 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code YL6Z7HBG.</x:v>
+        <x:v>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 21.94 mg. Client: Tomcat Peptides. Accession 2608250163; received 08/25/2026; reported 08/29/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -22299,25 +22820,25 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" t="str">
-        <x:v>COA-0084</x:v>
+        <x:v>COA-0045</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>CJC-1295</x:v>
       </x:c>
       <x:c r="D44" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>GHRH analog</x:v>
       </x:c>
       <x:c r="E44" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F44" t="n">
-        <x:v>21.1</x:v>
+        <x:v>10.52</x:v>
       </x:c>
       <x:c r="G44" t="n">
-        <x:v>0.05500000000000007</x:v>
+        <x:v>0.051999999999999956</x:v>
       </x:c>
       <x:c r="H44" t="n">
-        <x:v>99.71</x:v>
+        <x:v>99.72</x:v>
       </x:c>
       <x:c r="I44" t="str">
         <x:v>Overfilled</x:v>
@@ -22325,8 +22846,8 @@
       <x:c r="J44" t="str">
         <x:v>ILS Labs</x:v>
       </x:c>
-      <x:c r="K44" t="str">
-        <x:v>08/17/2026</x:v>
+      <x:c r="K44" t="n">
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="L44" t="str">
         <x:v>Not Listed</x:v>
@@ -22335,7 +22856,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N44" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.71%; net content 21.1 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code AGBSBU2E.</x:v>
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -22343,43 +22864,43 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" t="str">
-        <x:v>COA-0007</x:v>
+        <x:v>COA-0084</x:v>
       </x:c>
       <x:c r="C45" t="str">
         <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D45" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E45" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F45" t="n">
-        <x:v>26</x:v>
+        <x:v>21.1</x:v>
       </x:c>
       <x:c r="G45" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.05500000000000007</x:v>
       </x:c>
       <x:c r="H45" t="n">
-        <x:v>99.7</x:v>
+        <x:v>99.71</x:v>
       </x:c>
       <x:c r="I45" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J45" t="str">
-        <x:v>BT Labs</x:v>
-      </x:c>
-      <x:c r="K45" t="n">
-        <x:v>46133</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L45" t="str">
-        <x:v>Royal Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M45" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N45" t="str">
-        <x:v>20 mg label; 130.1% potency</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.71%; net content 21.1 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code AGBSBU2E.</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -22387,43 +22908,43 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" t="str">
-        <x:v>COA-0008</x:v>
+        <x:v>COA-0075</x:v>
       </x:c>
       <x:c r="C46" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Melanotan II</x:v>
       </x:c>
       <x:c r="D46" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Pigmentation / Research</x:v>
       </x:c>
       <x:c r="E46" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F46" t="n">
-        <x:v>46.6</x:v>
+        <x:v>10.34</x:v>
       </x:c>
       <x:c r="G46" t="n">
-        <x:v>0.165</x:v>
+        <x:v>0.03399999999999999</x:v>
       </x:c>
       <x:c r="H46" t="n">
-        <x:v>99.7</x:v>
+        <x:v>99.71</x:v>
       </x:c>
       <x:c r="I46" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J46" t="str">
-        <x:v>BT Labs</x:v>
-      </x:c>
-      <x:c r="K46" t="n">
-        <x:v>46106</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L46" t="str">
-        <x:v>Gray</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M46" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N46" t="str">
-        <x:v>40 mg label; 116.4% potency</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.71%; net content 10.34 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code YL6Z7HBG.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -22475,22 +22996,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" t="str">
-        <x:v>COA-0096</x:v>
+        <x:v>COA-0008</x:v>
       </x:c>
       <x:c r="C48" t="str">
-        <x:v>KLOW</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D48" t="str">
-        <x:v>Recovery / Blend</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E48" t="n">
-        <x:v>80</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F48" t="n">
-        <x:v>87.5</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="G48" t="n">
-        <x:v>0.09375</x:v>
+        <x:v>0.165</x:v>
       </x:c>
       <x:c r="H48" t="n">
         <x:v>99.7</x:v>
@@ -22499,19 +23020,19 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J48" t="str">
-        <x:v>BTLabs</x:v>
-      </x:c>
-      <x:c r="K48" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>BT Labs</x:v>
+      </x:c>
+      <x:c r="K48" t="n">
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L48" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Gray</x:v>
       </x:c>
       <x:c r="M48" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N48" t="str">
-        <x:v>Issued 2026-08-26. Components GHK-Cu 54.8mg, KPV 10.5mg, BPC-157 10.2mg, TB-500 12mg; total peptide 87.5mg. Gross powder mass 197.4mg includes excipients and is NOT peptide content. FTIR confirms composition. No microbial/endotoxin testing provided.</x:v>
+        <x:v>40 mg label; 116.4% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -22519,43 +23040,43 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" t="str">
-        <x:v>COA-0094</x:v>
+        <x:v>COA-0007</x:v>
       </x:c>
       <x:c r="C49" t="str">
-        <x:v>CJC-1295 No DAC / Ipamorelin</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D49" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E49" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F49" t="n">
-        <x:v>9.99</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G49" t="n">
-        <x:v>-0.001</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="H49" t="n">
-        <x:v>99.69</x:v>
+        <x:v>99.7</x:v>
       </x:c>
       <x:c r="I49" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J49" t="str">
-        <x:v>Freedom Diagnostics</x:v>
-      </x:c>
-      <x:c r="K49" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>BT Labs</x:v>
+      </x:c>
+      <x:c r="K49" t="n">
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="L49" t="str">
-        <x:v>Green</x:v>
+        <x:v>Royal Blue</x:v>
       </x:c>
       <x:c r="M49" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N49" t="str">
-        <x:v>Blend is CJC-1295 No DAC 5mg + Ipamorelin 5mg. Mean content: CJC 4.91mg + Ipamorelin 5.08mg. Samples: purity 99.66% / 99.72%; component contents 5.00 + 5.17mg / 4.82 + 5.00mg. Endotoxin, microbial PCR and elemental impurities pass; no fentanyl detected.</x:v>
+        <x:v>20 mg label; 130.1% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -22563,43 +23084,43 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" t="str">
-        <x:v>COA-0044</x:v>
+        <x:v>COA-0096</x:v>
       </x:c>
       <x:c r="C50" t="str">
-        <x:v>Eloralintide</x:v>
+        <x:v>KLOW</x:v>
       </x:c>
       <x:c r="D50" t="str">
-        <x:v>Amylin / Weight</x:v>
+        <x:v>Recovery / Blend</x:v>
       </x:c>
       <x:c r="E50" t="n">
-        <x:v>5</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F50" t="n">
-        <x:v>4.63</x:v>
+        <x:v>87.5</x:v>
       </x:c>
       <x:c r="G50" t="n">
-        <x:v>-0.07400000000000002</x:v>
+        <x:v>0.09375</x:v>
       </x:c>
       <x:c r="H50" t="n">
-        <x:v>99.67</x:v>
+        <x:v>99.7</x:v>
       </x:c>
       <x:c r="I50" t="str">
-        <x:v>Underfilled</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J50" t="str">
-        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
-      </x:c>
-      <x:c r="K50" t="n">
-        <x:v>46234</x:v>
+        <x:v>BTLabs</x:v>
+      </x:c>
+      <x:c r="K50" t="str">
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="L50" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M50" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N50" t="str">
-        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+        <x:v>Issued 2026-08-26. Components GHK-Cu 54.8mg, KPV 10.5mg, BPC-157 10.2mg, TB-500 12mg; total peptide 87.5mg. Gross powder mass 197.4mg includes excipients and is NOT peptide content. FTIR confirms composition. No microbial/endotoxin testing provided.</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -22607,43 +23128,43 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" t="str">
-        <x:v>COA-0003</x:v>
+        <x:v>COA-0094</x:v>
       </x:c>
       <x:c r="C51" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>CJC-1295 No DAC / Ipamorelin</x:v>
       </x:c>
       <x:c r="D51" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E51" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F51" t="n">
-        <x:v>6.63</x:v>
+        <x:v>9.99</x:v>
       </x:c>
       <x:c r="G51" t="n">
-        <x:v>0.326</x:v>
+        <x:v>-0.001</x:v>
       </x:c>
       <x:c r="H51" t="n">
-        <x:v>99.654</x:v>
+        <x:v>99.69</x:v>
       </x:c>
       <x:c r="I51" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J51" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K51" t="n">
-        <x:v>46174</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K51" t="str">
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="L51" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Green</x:v>
       </x:c>
       <x:c r="M51" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N51" t="str">
-        <x:v>Heavy metals negative; endotoxin pass</x:v>
+        <x:v>Blend is CJC-1295 No DAC 5mg + Ipamorelin 5mg. Mean content: CJC 4.91mg + Ipamorelin 5.08mg. Samples: purity 99.66% / 99.72%; component contents 5.00 + 5.17mg / 4.82 + 5.00mg. Endotoxin, microbial PCR and elemental impurities pass; no fentanyl detected.</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -22651,43 +23172,43 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B52" t="str">
-        <x:v>COA-0032</x:v>
+        <x:v>COA-0044</x:v>
       </x:c>
       <x:c r="C52" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Eloralintide</x:v>
       </x:c>
       <x:c r="D52" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Amylin / Weight</x:v>
       </x:c>
       <x:c r="E52" t="n">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F52" t="n">
-        <x:v>15.53</x:v>
+        <x:v>4.63</x:v>
       </x:c>
       <x:c r="G52" t="n">
-        <x:v>0.035333333333333335</x:v>
+        <x:v>-0.07400000000000002</x:v>
       </x:c>
       <x:c r="H52" t="n">
-        <x:v>99.642</x:v>
+        <x:v>99.67</x:v>
       </x:c>
       <x:c r="I52" t="str">
-        <x:v>On label</x:v>
+        <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="J52" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K52" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K52" t="n">
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="L52" t="str">
-        <x:v>Black</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M52" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N52" t="str">
-        <x:v>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</x:v>
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -22695,25 +23216,25 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B53" t="str">
-        <x:v>COA-0033</x:v>
+        <x:v>COA-0003</x:v>
       </x:c>
       <x:c r="C53" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D53" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E53" t="n">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F53" t="n">
-        <x:v>33.24</x:v>
+        <x:v>6.63</x:v>
       </x:c>
       <x:c r="G53" t="n">
-        <x:v>0.10800000000000001</x:v>
+        <x:v>0.326</x:v>
       </x:c>
       <x:c r="H53" t="n">
-        <x:v>99.6</x:v>
+        <x:v>99.654</x:v>
       </x:c>
       <x:c r="I53" t="str">
         <x:v>Overfilled</x:v>
@@ -22721,17 +23242,17 @@
       <x:c r="J53" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
-      <x:c r="K53" t="str">
-        <x:v>2026-07-03</x:v>
+      <x:c r="K53" t="n">
+        <x:v>46174</x:v>
       </x:c>
       <x:c r="L53" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M53" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N53" t="str">
-        <x:v>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
+        <x:v>Heavy metals negative; endotoxin pass</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -22739,43 +23260,43 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B54" t="str">
-        <x:v>COA-0047</x:v>
+        <x:v>COA-0032</x:v>
       </x:c>
       <x:c r="C54" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="D54" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E54" t="n">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F54" t="n">
-        <x:v>63.37</x:v>
+        <x:v>15.53</x:v>
       </x:c>
       <x:c r="G54" t="n">
-        <x:v>0.05616666666666662</x:v>
+        <x:v>0.035333333333333335</x:v>
       </x:c>
       <x:c r="H54" t="n">
-        <x:v>99.59</x:v>
+        <x:v>99.642</x:v>
       </x:c>
       <x:c r="I54" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J54" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K54" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L54" t="str">
-        <x:v>Red</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M54" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N54" t="str">
-        <x:v>Identity confirmed as Retatrutide by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
+        <x:v>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -22783,43 +23304,43 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B55" t="str">
-        <x:v>COA-0020</x:v>
+        <x:v>COA-0033</x:v>
       </x:c>
       <x:c r="C55" t="str">
-        <x:v>KPV</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D55" t="str">
-        <x:v>Other</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E55" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F55" t="n">
-        <x:v>12.19</x:v>
+        <x:v>33.24</x:v>
       </x:c>
       <x:c r="G55" t="n">
-        <x:v>0.2189999999999999</x:v>
+        <x:v>0.10800000000000001</x:v>
       </x:c>
       <x:c r="H55" t="n">
-        <x:v>99.589</x:v>
+        <x:v>99.6</x:v>
       </x:c>
       <x:c r="I55" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J55" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K55" t="n">
-        <x:v>46057</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K55" t="str">
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L55" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M55" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N55" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -22827,7 +23348,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B56" t="str">
-        <x:v>COA-0031</x:v>
+        <x:v>COA-0047</x:v>
       </x:c>
       <x:c r="C56" t="str">
         <x:v>Retatrutide</x:v>
@@ -22836,34 +23357,34 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E56" t="n">
-        <x:v>30</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F56" t="n">
-        <x:v>33.77</x:v>
+        <x:v>63.37</x:v>
       </x:c>
       <x:c r="G56" t="n">
-        <x:v>0.12566666666666668</x:v>
+        <x:v>0.05616666666666662</x:v>
       </x:c>
       <x:c r="H56" t="n">
-        <x:v>99.58</x:v>
+        <x:v>99.59</x:v>
       </x:c>
       <x:c r="I56" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J56" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
       <x:c r="L56" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="M56" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N56" t="str">
-        <x:v>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Identity confirmed as Retatrutide by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -22871,34 +23392,34 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B57" t="str">
-        <x:v>COA-0081</x:v>
+        <x:v>COA-0020</x:v>
       </x:c>
       <x:c r="C57" t="str">
-        <x:v>Semax</x:v>
+        <x:v>KPV</x:v>
       </x:c>
       <x:c r="D57" t="str">
-        <x:v>Nootropic / Research</x:v>
+        <x:v>Other</x:v>
       </x:c>
       <x:c r="E57" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F57" t="n">
-        <x:v>10.5</x:v>
+        <x:v>12.19</x:v>
       </x:c>
       <x:c r="G57" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.2189999999999999</x:v>
       </x:c>
       <x:c r="H57" t="n">
-        <x:v>99.58</x:v>
+        <x:v>99.589</x:v>
       </x:c>
       <x:c r="I57" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J57" t="str">
-        <x:v>ILS Labs</x:v>
-      </x:c>
-      <x:c r="K57" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K57" t="n">
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L57" t="str">
         <x:v>Not Listed</x:v>
@@ -22907,7 +23428,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N57" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.58%; net content 10.5 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6293KLTS.</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -22959,43 +23480,43 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B59" t="str">
-        <x:v>COA-0040</x:v>
+        <x:v>COA-0081</x:v>
       </x:c>
       <x:c r="C59" t="str">
-        <x:v>BPC-157</x:v>
+        <x:v>Semax</x:v>
       </x:c>
       <x:c r="D59" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Nootropic / Research</x:v>
       </x:c>
       <x:c r="E59" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F59" t="n">
-        <x:v>5.13</x:v>
+        <x:v>10.5</x:v>
       </x:c>
       <x:c r="G59" t="n">
-        <x:v>0.025999999999999978</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="H59" t="n">
-        <x:v>99.57</x:v>
+        <x:v>99.58</x:v>
       </x:c>
       <x:c r="I59" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J59" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K59" t="n">
-        <x:v>46239</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K59" t="str">
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L59" t="str">
-        <x:v>Green</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M59" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N59" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.58%; net content 10.5 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6293KLTS.</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -23003,34 +23524,34 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B60" t="str">
-        <x:v>COA-0080</x:v>
+        <x:v>COA-0031</x:v>
       </x:c>
       <x:c r="C60" t="str">
-        <x:v>Selank</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D60" t="str">
-        <x:v>Nootropic / Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E60" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F60" t="n">
-        <x:v>10.66</x:v>
+        <x:v>33.77</x:v>
       </x:c>
       <x:c r="G60" t="n">
-        <x:v>0.06600000000000002</x:v>
+        <x:v>0.12566666666666668</x:v>
       </x:c>
       <x:c r="H60" t="n">
-        <x:v>99.57</x:v>
+        <x:v>99.58</x:v>
       </x:c>
       <x:c r="I60" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J60" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Testides</x:v>
       </x:c>
       <x:c r="K60" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L60" t="str">
         <x:v>Not Listed</x:v>
@@ -23039,7 +23560,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N60" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.57%; net content 10.66 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code JBYELVFU.</x:v>
+        <x:v>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -23047,43 +23568,43 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B61" t="str">
-        <x:v>COA-0026</x:v>
+        <x:v>COA-0080</x:v>
       </x:c>
       <x:c r="C61" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Selank</x:v>
       </x:c>
       <x:c r="D61" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Nootropic / Research</x:v>
       </x:c>
       <x:c r="E61" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F61" t="n">
-        <x:v>42.53</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G61" t="n">
-        <x:v>0.06325</x:v>
+        <x:v>0.06600000000000002</x:v>
       </x:c>
       <x:c r="H61" t="n">
-        <x:v>99.569</x:v>
+        <x:v>99.57</x:v>
       </x:c>
       <x:c r="I61" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J61" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K61" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L61" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M61" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N61" t="str">
-        <x:v>Blue cap Retatrutide 40mg</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.57%; net content 10.66 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code JBYELVFU.</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -23091,43 +23612,43 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B62" t="str">
-        <x:v>COA-0060</x:v>
+        <x:v>COA-0040</x:v>
       </x:c>
       <x:c r="C62" t="str">
-        <x:v>Semax</x:v>
+        <x:v>BPC-157</x:v>
       </x:c>
       <x:c r="D62" t="str">
-        <x:v>Nootropic / Research</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E62" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F62" t="n">
-        <x:v>9.65</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="G62" t="n">
-        <x:v>-0.034999999999999996</x:v>
+        <x:v>0.025999999999999978</x:v>
       </x:c>
       <x:c r="H62" t="n">
-        <x:v>99.568</x:v>
+        <x:v>99.57</x:v>
       </x:c>
       <x:c r="I62" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J62" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K62" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K62" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L62" t="str">
-        <x:v>Black</x:v>
+        <x:v>Green</x:v>
       </x:c>
       <x:c r="M62" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N62" t="str">
-        <x:v>Identity confirmed as Semax by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.328% / 9.56 mg; vial 2: 99.808% / 9.74 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -23135,7 +23656,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B63" t="str">
-        <x:v>COA-0025</x:v>
+        <x:v>COA-0026</x:v>
       </x:c>
       <x:c r="C63" t="str">
         <x:v>Retatrutide</x:v>
@@ -23144,16 +23665,16 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E63" t="n">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F63" t="n">
-        <x:v>33.31</x:v>
+        <x:v>42.53</x:v>
       </x:c>
       <x:c r="G63" t="n">
-        <x:v>0.1103333333333333</x:v>
+        <x:v>0.06325</x:v>
       </x:c>
       <x:c r="H63" t="n">
-        <x:v>99.563</x:v>
+        <x:v>99.569</x:v>
       </x:c>
       <x:c r="I63" t="str">
         <x:v>Overfilled</x:v>
@@ -23165,13 +23686,13 @@
         <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="L63" t="str">
-        <x:v>Transparent</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M63" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N63" t="str">
-        <x:v>Transparent cap Retatrutide 30mg</x:v>
+        <x:v>Blue cap Retatrutide 40mg</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -23179,25 +23700,25 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B64" t="str">
-        <x:v>COA-0046</x:v>
+        <x:v>COA-0060</x:v>
       </x:c>
       <x:c r="C64" t="str">
-        <x:v>NAD+</x:v>
+        <x:v>Semax</x:v>
       </x:c>
       <x:c r="D64" t="str">
-        <x:v>Metabolic / Cellular Energy</x:v>
+        <x:v>Nootropic / Research</x:v>
       </x:c>
       <x:c r="E64" t="n">
-        <x:v>500</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F64" t="n">
-        <x:v>488.47</x:v>
+        <x:v>9.65</x:v>
       </x:c>
       <x:c r="G64" t="n">
-        <x:v>-0.023059999999999945</x:v>
+        <x:v>-0.034999999999999996</x:v>
       </x:c>
       <x:c r="H64" t="n">
-        <x:v>99.549</x:v>
+        <x:v>99.568</x:v>
       </x:c>
       <x:c r="I64" t="str">
         <x:v>On label</x:v>
@@ -23205,8 +23726,8 @@
       <x:c r="J64" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
-      <x:c r="K64" t="n">
-        <x:v>46232</x:v>
+      <x:c r="K64" t="str">
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="L64" t="str">
         <x:v>Black</x:v>
@@ -23215,7 +23736,7 @@
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N64" t="str">
-        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
+        <x:v>Identity confirmed as Semax by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.328% / 9.56 mg; vial 2: 99.808% / 9.74 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -23223,43 +23744,43 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B65" t="str">
-        <x:v>COA-0079</x:v>
+        <x:v>COA-0025</x:v>
       </x:c>
       <x:c r="C65" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D65" t="str">
-        <x:v>Metabolic / Mitochondrial Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E65" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F65" t="n">
-        <x:v>10.7</x:v>
+        <x:v>33.31</x:v>
       </x:c>
       <x:c r="G65" t="n">
-        <x:v>0.06999999999999992</x:v>
+        <x:v>0.1103333333333333</x:v>
       </x:c>
       <x:c r="H65" t="n">
-        <x:v>99.53</x:v>
+        <x:v>99.563</x:v>
       </x:c>
       <x:c r="I65" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J65" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="L65" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Transparent</x:v>
       </x:c>
       <x:c r="M65" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N65" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.53%; net content 10.7 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code KSU4VSE7.</x:v>
+        <x:v>Transparent cap Retatrutide 30mg</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -23267,43 +23788,43 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B66" t="str">
-        <x:v>COA-0038</x:v>
+        <x:v>COA-0046</x:v>
       </x:c>
       <x:c r="C66" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="D66" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Metabolic / Cellular Energy</x:v>
       </x:c>
       <x:c r="E66" t="n">
-        <x:v>10</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="F66" t="n">
-        <x:v>10.09</x:v>
+        <x:v>488.47</x:v>
       </x:c>
       <x:c r="G66" t="n">
-        <x:v>0.008999999999999985</x:v>
+        <x:v>-0.023059999999999945</x:v>
       </x:c>
       <x:c r="H66" t="n">
-        <x:v>99.52</x:v>
+        <x:v>99.549</x:v>
       </x:c>
       <x:c r="I66" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J66" t="str">
-        <x:v>SteriGenix</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K66" t="n">
-        <x:v>46239</x:v>
+        <x:v>46232</x:v>
       </x:c>
       <x:c r="L66" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M66" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N66" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -23311,34 +23832,34 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B67" t="str">
-        <x:v>COA-0001</x:v>
+        <x:v>COA-0079</x:v>
       </x:c>
       <x:c r="C67" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="D67" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Metabolic / Mitochondrial Research</x:v>
       </x:c>
       <x:c r="E67" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F67" t="n">
-        <x:v>11.8</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="G67" t="n">
-        <x:v>0.1800000000000001</x:v>
+        <x:v>0.06999999999999992</x:v>
       </x:c>
       <x:c r="H67" t="n">
-        <x:v>99.516</x:v>
+        <x:v>99.53</x:v>
       </x:c>
       <x:c r="I67" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J67" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K67" t="n">
-        <x:v>46156</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K67" t="str">
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L67" t="str">
         <x:v>Not Listed</x:v>
@@ -23347,7 +23868,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N67" t="str">
-        <x:v>RT10 - common GLP-1 blind test; overfilled</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.53%; net content 10.7 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code KSU4VSE7.</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -23355,43 +23876,43 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B68" t="str">
-        <x:v>COA-0059</x:v>
+        <x:v>COA-0038</x:v>
       </x:c>
       <x:c r="C68" t="str">
-        <x:v>Glutathione</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D68" t="str">
-        <x:v>Antioxidant / Cellular Support</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E68" t="n">
-        <x:v>1500</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F68" t="n">
-        <x:v>1478.47</x:v>
+        <x:v>10.09</x:v>
       </x:c>
       <x:c r="G68" t="n">
-        <x:v>-0.014353333333333334</x:v>
+        <x:v>0.008999999999999985</x:v>
       </x:c>
       <x:c r="H68" t="n">
-        <x:v>99.513</x:v>
+        <x:v>99.52</x:v>
       </x:c>
       <x:c r="I68" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J68" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K68" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K68" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L68" t="str">
-        <x:v>Red</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M68" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N68" t="str">
-        <x:v>Identity confirmed as Glutathione by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.246% / 1464.59 mg; vial 2: 99.781% / 1492.36 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -23399,7 +23920,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B69" t="str">
-        <x:v>COA-0006</x:v>
+        <x:v>COA-0001</x:v>
       </x:c>
       <x:c r="C69" t="str">
         <x:v>Retatrutide</x:v>
@@ -23407,22 +23928,26 @@
       <x:c r="D69" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
-      <x:c r="E69"/>
+      <x:c r="E69" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="F69" t="n">
-        <x:v>22.47</x:v>
-      </x:c>
-      <x:c r="G69"/>
+        <x:v>11.8</x:v>
+      </x:c>
+      <x:c r="G69" t="n">
+        <x:v>0.1800000000000001</x:v>
+      </x:c>
       <x:c r="H69" t="n">
-        <x:v>99.5</x:v>
+        <x:v>99.516</x:v>
       </x:c>
       <x:c r="I69" t="str">
-        <x:v>Review</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J69" t="str">
-        <x:v>Aminos Analytics</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K69" t="n">
-        <x:v>46146</x:v>
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L69" t="str">
         <x:v>Not Listed</x:v>
@@ -23431,7 +23956,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N69" t="str">
-        <x:v>Labeled quantity unclear from image</x:v>
+        <x:v>RT10 - common GLP-1 blind test; overfilled</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -23439,43 +23964,43 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B70" t="str">
-        <x:v>COA-0004</x:v>
+        <x:v>COA-0059</x:v>
       </x:c>
       <x:c r="C70" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Glutathione</x:v>
       </x:c>
       <x:c r="D70" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Antioxidant / Cellular Support</x:v>
       </x:c>
       <x:c r="E70" t="n">
-        <x:v>15</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="F70" t="n">
-        <x:v>17.93</x:v>
+        <x:v>1478.47</x:v>
       </x:c>
       <x:c r="G70" t="n">
-        <x:v>0.1953333333333333</x:v>
+        <x:v>-0.014353333333333334</x:v>
       </x:c>
       <x:c r="H70" t="n">
-        <x:v>99.491</x:v>
+        <x:v>99.513</x:v>
       </x:c>
       <x:c r="I70" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J70" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
-      <x:c r="K70" t="n">
-        <x:v>46175</x:v>
+      <x:c r="K70" t="str">
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="L70" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="M70" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N70" t="str">
-        <x:v>Heavy metals negative; endotoxin pass</x:v>
+        <x:v>Identity confirmed as Glutathione by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.246% / 1464.59 mg; vial 2: 99.781% / 1492.36 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -23483,7 +24008,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B71" t="str">
-        <x:v>COA-0030</x:v>
+        <x:v>COA-0105</x:v>
       </x:c>
       <x:c r="C71" t="str">
         <x:v>Retatrutide</x:v>
@@ -23492,34 +24017,34 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E71" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F71" t="n">
-        <x:v>21.4</x:v>
+        <x:v>12.76</x:v>
       </x:c>
       <x:c r="G71" t="n">
-        <x:v>0.06999999999999999</x:v>
+        <x:v>0.27599999999999997</x:v>
       </x:c>
       <x:c r="H71" t="n">
-        <x:v>99.49</x:v>
+        <x:v>99.51</x:v>
       </x:c>
       <x:c r="I71" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J71" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="K71" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-09-18</x:v>
       </x:c>
       <x:c r="L71" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Not listed</x:v>
       </x:c>
       <x:c r="M71" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Not listed</x:v>
       </x:c>
       <x:c r="N71" t="str">
-        <x:v>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -23527,43 +24052,39 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B72" t="str">
-        <x:v>COA-0051</x:v>
+        <x:v>COA-0006</x:v>
       </x:c>
       <x:c r="C72" t="str">
-        <x:v>DSIP</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D72" t="str">
-        <x:v>Sleep / Research</x:v>
-      </x:c>
-      <x:c r="E72" t="n">
-        <x:v>10</x:v>
-      </x:c>
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="E72"/>
       <x:c r="F72" t="n">
-        <x:v>10.16</x:v>
-      </x:c>
-      <x:c r="G72" t="n">
-        <x:v>0.016000000000000014</x:v>
-      </x:c>
+        <x:v>22.47</x:v>
+      </x:c>
+      <x:c r="G72"/>
       <x:c r="H72" t="n">
-        <x:v>99.464</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="I72" t="str">
-        <x:v>On label</x:v>
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="J72" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K72" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>Aminos Analytics</x:v>
+      </x:c>
+      <x:c r="K72" t="n">
+        <x:v>46146</x:v>
       </x:c>
       <x:c r="L72" t="str">
-        <x:v>Red</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M72" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N72" t="str">
-        <x:v>Identity confirmed as DSIP by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
+        <x:v>Labeled quantity unclear from image</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -23571,43 +24092,43 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B73" t="str">
-        <x:v>COA-0052</x:v>
+        <x:v>COA-0004</x:v>
       </x:c>
       <x:c r="C73" t="str">
-        <x:v>CJC-1295 No DAC / Ipamorelin</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D73" t="str">
-        <x:v>GHRH / GH Secretagogue Blend</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E73" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F73" t="n">
-        <x:v>10.42</x:v>
+        <x:v>17.93</x:v>
       </x:c>
       <x:c r="G73" t="n">
-        <x:v>0.042</x:v>
+        <x:v>0.1953333333333333</x:v>
       </x:c>
       <x:c r="H73" t="n">
-        <x:v>99.446</x:v>
+        <x:v>99.491</x:v>
       </x:c>
       <x:c r="I73" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J73" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K73" t="n">
-        <x:v>46242</x:v>
+        <x:v>46175</x:v>
       </x:c>
       <x:c r="L73" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M73" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N73" t="str">
-        <x:v>Blend identity confirmed by LC-MS. Component analysis: Ipamorelin labeled 5 mg / measured 5.84 mg; CJC-1295 No DAC labeled 5 mg / measured 4.71 mg. Endotoxin PASS; microbial sterility: No Growth.</x:v>
+        <x:v>Heavy metals negative; endotoxin pass</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -23615,7 +24136,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B74" t="str">
-        <x:v>COA-0043</x:v>
+        <x:v>COA-0030</x:v>
       </x:c>
       <x:c r="C74" t="str">
         <x:v>Retatrutide</x:v>
@@ -23624,34 +24145,34 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E74" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F74" t="n">
-        <x:v>10.36</x:v>
+        <x:v>21.4</x:v>
       </x:c>
       <x:c r="G74" t="n">
-        <x:v>0.03599999999999994</x:v>
+        <x:v>0.06999999999999999</x:v>
       </x:c>
       <x:c r="H74" t="n">
-        <x:v>99.41</x:v>
+        <x:v>99.49</x:v>
       </x:c>
       <x:c r="I74" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J74" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K74" t="n">
-        <x:v>46239</x:v>
+        <x:v>Testides</x:v>
+      </x:c>
+      <x:c r="K74" t="str">
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L74" t="str">
-        <x:v>Clear</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M74" t="str">
-        <x:v>Copper</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N74" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -23659,43 +24180,43 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B75" t="str">
-        <x:v>COA-0077</x:v>
+        <x:v>COA-0051</x:v>
       </x:c>
       <x:c r="C75" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>DSIP</x:v>
       </x:c>
       <x:c r="D75" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>Sleep / Research</x:v>
       </x:c>
       <x:c r="E75" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F75" t="n">
-        <x:v>10.64</x:v>
+        <x:v>10.16</x:v>
       </x:c>
       <x:c r="G75" t="n">
-        <x:v>0.06400000000000006</x:v>
+        <x:v>0.016000000000000014</x:v>
       </x:c>
       <x:c r="H75" t="n">
-        <x:v>99.4</x:v>
+        <x:v>99.464</x:v>
       </x:c>
       <x:c r="I75" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J75" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
       <x:c r="L75" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="M75" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N75" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.4%; net content 10.64 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6DGZ93CS.</x:v>
+        <x:v>Identity confirmed as DSIP by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -23703,43 +24224,43 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B76" t="str">
-        <x:v>COA-0029</x:v>
+        <x:v>COA-0052</x:v>
       </x:c>
       <x:c r="C76" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>CJC-1295 No DAC / Ipamorelin</x:v>
       </x:c>
       <x:c r="D76" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>GHRH / GH Secretagogue Blend</x:v>
       </x:c>
       <x:c r="E76" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F76" t="n">
-        <x:v>45.03</x:v>
+        <x:v>10.42</x:v>
       </x:c>
       <x:c r="G76" t="n">
-        <x:v>0.12575</x:v>
+        <x:v>0.042</x:v>
       </x:c>
       <x:c r="H76" t="n">
-        <x:v>99.39</x:v>
+        <x:v>99.446</x:v>
       </x:c>
       <x:c r="I76" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J76" t="str">
-        <x:v>Testides</x:v>
-      </x:c>
-      <x:c r="K76" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K76" t="n">
+        <x:v>46242</x:v>
       </x:c>
       <x:c r="L76" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M76" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N76" t="str">
-        <x:v>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Blend identity confirmed by LC-MS. Component analysis: Ipamorelin labeled 5 mg / measured 5.84 mg; CJC-1295 No DAC labeled 5 mg / measured 4.71 mg. Endotoxin PASS; microbial sterility: No Growth.</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -23747,43 +24268,43 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B77" t="str">
-        <x:v>COA-0098</x:v>
+        <x:v>COA-0043</x:v>
       </x:c>
       <x:c r="C77" t="str">
-        <x:v>NAD+</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D77" t="str">
-        <x:v>Cellular Support</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E77" t="n">
-        <x:v>1000</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F77" t="n">
-        <x:v>1006.39</x:v>
+        <x:v>10.36</x:v>
       </x:c>
       <x:c r="G77" t="n">
-        <x:v>0.00639</x:v>
+        <x:v>0.03599999999999994</x:v>
       </x:c>
       <x:c r="H77" t="n">
-        <x:v>99.38</x:v>
+        <x:v>99.41</x:v>
       </x:c>
       <x:c r="I77" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J77" t="str">
-        <x:v>PurePoint Analytical</x:v>
-      </x:c>
-      <x:c r="K77" t="str">
-        <x:v>2026-09-17</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K77" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L77" t="str">
-        <x:v>Black</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="M77" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Copper</x:v>
       </x:c>
       <x:c r="N77" t="str">
-        <x:v>Issued 2026-09-21. Batch average 99.38% / 1006.39mg; vial 1 99.77% / 1009.67mg; vial 2 98.98% / 1003.11mg. pH 6.10. Identity confirmed; heavy metals, endotoxin, sterility and fentanyl screens pass.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -23791,34 +24312,34 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B78" t="str">
-        <x:v>COA-0002</x:v>
+        <x:v>COA-0077</x:v>
       </x:c>
       <x:c r="C78" t="str">
         <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D78" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E78" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F78" t="n">
-        <x:v>10</x:v>
+        <x:v>10.64</x:v>
       </x:c>
       <x:c r="G78" t="n">
-        <x:v>0</x:v>
+        <x:v>0.06400000000000006</x:v>
       </x:c>
       <x:c r="H78" t="n">
-        <x:v>99.369</x:v>
+        <x:v>99.4</x:v>
       </x:c>
       <x:c r="I78" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J78" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K78" t="n">
-        <x:v>46057</x:v>
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K78" t="str">
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L78" t="str">
         <x:v>Not Listed</x:v>
@@ -23827,7 +24348,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N78" t="str">
-        <x:v>On label</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.4%; net content 10.64 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6DGZ93CS.</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -23835,43 +24356,43 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B79" t="str">
-        <x:v>COA-0049</x:v>
+        <x:v>COA-0104</x:v>
       </x:c>
       <x:c r="C79" t="str">
-        <x:v>5-Amino-1MQ</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D79" t="str">
-        <x:v>Metabolic / Research</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E79" t="n">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F79" t="n">
-        <x:v>51.88</x:v>
+        <x:v>10.94</x:v>
       </x:c>
       <x:c r="G79" t="n">
-        <x:v>0.03760000000000005</x:v>
+        <x:v>0.094</x:v>
       </x:c>
       <x:c r="H79" t="n">
-        <x:v>99.369</x:v>
+        <x:v>99.3905</x:v>
       </x:c>
       <x:c r="I79" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J79" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-10-27</x:v>
       </x:c>
       <x:c r="L79" t="str">
-        <x:v>Red</x:v>
+        <x:v>Not listed</x:v>
       </x:c>
       <x:c r="M79" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not listed</x:v>
       </x:c>
       <x:c r="N79" t="str">
-        <x:v>Identity confirmed as 5-Amino-1MQ by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -23879,34 +24400,34 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B80" t="str">
-        <x:v>COA-0083</x:v>
+        <x:v>COA-0029</x:v>
       </x:c>
       <x:c r="C80" t="str">
-        <x:v>Tesamorelin</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D80" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E80" t="n">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F80" t="n">
-        <x:v>10.24</x:v>
+        <x:v>45.03</x:v>
       </x:c>
       <x:c r="G80" t="n">
-        <x:v>0.02400000000000002</x:v>
+        <x:v>0.12575</x:v>
       </x:c>
       <x:c r="H80" t="n">
-        <x:v>99.36</x:v>
+        <x:v>99.39</x:v>
       </x:c>
       <x:c r="I80" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J80" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Testides</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L80" t="str">
         <x:v>Not Listed</x:v>
@@ -23915,7 +24436,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N80" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.36%; net content 10.24 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code U5SWVSHY.</x:v>
+        <x:v>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -23923,43 +24444,43 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B81" t="str">
-        <x:v>COA-0042</x:v>
+        <x:v>COA-0098</x:v>
       </x:c>
       <x:c r="C81" t="str">
-        <x:v>Ipamorelin</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="D81" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Cellular Support</x:v>
       </x:c>
       <x:c r="E81" t="n">
-        <x:v>5</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="F81" t="n">
-        <x:v>5.17</x:v>
+        <x:v>1006.39</x:v>
       </x:c>
       <x:c r="G81" t="n">
-        <x:v>0.03399999999999999</x:v>
+        <x:v>0.00639</x:v>
       </x:c>
       <x:c r="H81" t="n">
-        <x:v>99.34</x:v>
+        <x:v>99.38</x:v>
       </x:c>
       <x:c r="I81" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J81" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K81" t="n">
-        <x:v>46239</x:v>
+        <x:v>PurePoint Analytical</x:v>
+      </x:c>
+      <x:c r="K81" t="str">
+        <x:v>2026-09-17</x:v>
       </x:c>
       <x:c r="L81" t="str">
-        <x:v>White</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M81" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N81" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Issued 2026-09-21. Batch average 99.38% / 1006.39mg; vial 1 99.77% / 1009.67mg; vial 2 98.98% / 1003.11mg. pH 6.10. Identity confirmed; heavy metals, endotoxin, sterility and fentanyl screens pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -23967,25 +24488,25 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B82" t="str">
-        <x:v>COA-0061</x:v>
+        <x:v>COA-0049</x:v>
       </x:c>
       <x:c r="C82" t="str">
-        <x:v>Sermorelin</x:v>
+        <x:v>5-Amino-1MQ</x:v>
       </x:c>
       <x:c r="D82" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Metabolic / Research</x:v>
       </x:c>
       <x:c r="E82" t="n">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F82" t="n">
-        <x:v>10.41</x:v>
+        <x:v>51.88</x:v>
       </x:c>
       <x:c r="G82" t="n">
-        <x:v>0.040999999999999995</x:v>
+        <x:v>0.03760000000000005</x:v>
       </x:c>
       <x:c r="H82" t="n">
-        <x:v>99.335</x:v>
+        <x:v>99.369</x:v>
       </x:c>
       <x:c r="I82" t="str">
         <x:v>On label</x:v>
@@ -23994,16 +24515,16 @@
         <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
       <x:c r="L82" t="str">
-        <x:v>Green</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="M82" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N82" t="str">
-        <x:v>Identity confirmed as Sermorelin by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.266% / 10.31 mg; vial 2: 99.403% / 10.51 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed as 5-Amino-1MQ by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -24011,43 +24532,43 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B83" t="str">
-        <x:v>COA-0039</x:v>
+        <x:v>COA-0002</x:v>
       </x:c>
       <x:c r="C83" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D83" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E83" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F83" t="n">
-        <x:v>5.07</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G83" t="n">
-        <x:v>0.014000000000000058</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H83" t="n">
-        <x:v>99.32</x:v>
+        <x:v>99.369</x:v>
       </x:c>
       <x:c r="I83" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J83" t="str">
-        <x:v>SteriGenix</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K83" t="n">
-        <x:v>46239</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L83" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M83" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N83" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>On label</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -24055,43 +24576,43 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B84" t="str">
-        <x:v>COA-0048</x:v>
+        <x:v>COA-0083</x:v>
       </x:c>
       <x:c r="C84" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>Tesamorelin</x:v>
       </x:c>
       <x:c r="D84" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E84" t="n">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F84" t="n">
-        <x:v>51.52</x:v>
+        <x:v>10.24</x:v>
       </x:c>
       <x:c r="G84" t="n">
-        <x:v>0.030400000000000062</x:v>
+        <x:v>0.02400000000000002</x:v>
       </x:c>
       <x:c r="H84" t="n">
-        <x:v>99.32</x:v>
+        <x:v>99.36</x:v>
       </x:c>
       <x:c r="I84" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J84" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>08/17/2026</x:v>
       </x:c>
       <x:c r="L84" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M84" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N84" t="str">
-        <x:v>Identity confirmed as SS-31 by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.36%; net content 10.24 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code U5SWVSHY.</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -24099,43 +24620,43 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B85" t="str">
-        <x:v>COA-0074</x:v>
+        <x:v>COA-0042</x:v>
       </x:c>
       <x:c r="C85" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Ipamorelin</x:v>
       </x:c>
       <x:c r="D85" t="str">
-        <x:v>Metabolic / Mitochondrial Research</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E85" t="n">
-        <x:v>40</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F85" t="n">
-        <x:v>41.09</x:v>
+        <x:v>5.17</x:v>
       </x:c>
       <x:c r="G85" t="n">
-        <x:v>0.027250000000000087</x:v>
+        <x:v>0.03399999999999999</x:v>
       </x:c>
       <x:c r="H85" t="n">
-        <x:v>99.3</x:v>
+        <x:v>99.34</x:v>
       </x:c>
       <x:c r="I85" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J85" t="str">
-        <x:v>ILS Labs</x:v>
-      </x:c>
-      <x:c r="K85" t="str">
-        <x:v>08/17/2026</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K85" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L85" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>White</x:v>
       </x:c>
       <x:c r="M85" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N85" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.3%; net content 41.09 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code SQG57YUA.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -24143,43 +24664,43 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B86" t="str">
-        <x:v>COA-0076</x:v>
+        <x:v>COA-0061</x:v>
       </x:c>
       <x:c r="C86" t="str">
-        <x:v>NAD+</x:v>
+        <x:v>Sermorelin</x:v>
       </x:c>
       <x:c r="D86" t="str">
-        <x:v>Cellular / Metabolic Research</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E86" t="n">
-        <x:v>1000</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F86" t="n">
-        <x:v>1047.39</x:v>
+        <x:v>10.41</x:v>
       </x:c>
       <x:c r="G86" t="n">
-        <x:v>0.0473900000000001</x:v>
+        <x:v>0.040999999999999995</x:v>
       </x:c>
       <x:c r="H86" t="n">
-        <x:v>99.26</x:v>
+        <x:v>99.335</x:v>
       </x:c>
       <x:c r="I86" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J86" t="str">
-        <x:v>ILS Labs</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K86" t="str">
-        <x:v>08/18/2026</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="L86" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Green</x:v>
       </x:c>
       <x:c r="M86" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N86" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.26%; net content 1047.39 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code EKUVZRXB.</x:v>
+        <x:v>Identity confirmed as Sermorelin by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.266% / 10.31 mg; vial 2: 99.403% / 10.51 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -24187,43 +24708,43 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B87" t="str">
-        <x:v>COA-0053</x:v>
+        <x:v>COA-0048</x:v>
       </x:c>
       <x:c r="C87" t="str">
-        <x:v>GHK-Cu</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="D87" t="str">
-        <x:v>Cosmetic / Recovery</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E87" t="n">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F87" t="n">
-        <x:v>100.52</x:v>
+        <x:v>51.52</x:v>
       </x:c>
       <x:c r="G87" t="n">
-        <x:v>0.0052</x:v>
+        <x:v>0.030400000000000062</x:v>
       </x:c>
       <x:c r="H87" t="n">
-        <x:v>99.25</x:v>
+        <x:v>99.32</x:v>
       </x:c>
       <x:c r="I87" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J87" t="str">
-        <x:v>Freedom Diagnostics</x:v>
-      </x:c>
-      <x:c r="K87" t="n">
-        <x:v>46224</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K87" t="str">
+        <x:v>2026-07-29</x:v>
       </x:c>
       <x:c r="L87" t="str">
-        <x:v>Light Blue</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M87" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N87" t="str">
-        <x:v>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</x:v>
+        <x:v>Identity confirmed as SS-31 by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -24231,25 +24752,25 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B88" t="str">
-        <x:v>COA-0062</x:v>
+        <x:v>COA-0039</x:v>
       </x:c>
       <x:c r="C88" t="str">
-        <x:v>GHK-Cu</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="D88" t="str">
-        <x:v>Cosmetic / Recovery</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E88" t="n">
-        <x:v>50</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F88" t="n">
-        <x:v>52.48</x:v>
+        <x:v>5.07</x:v>
       </x:c>
       <x:c r="G88" t="n">
-        <x:v>0.0496</x:v>
+        <x:v>0.014000000000000058</x:v>
       </x:c>
       <x:c r="H88" t="n">
-        <x:v>99.25</x:v>
+        <x:v>99.32</x:v>
       </x:c>
       <x:c r="I88" t="str">
         <x:v>On label</x:v>
@@ -24257,8 +24778,8 @@
       <x:c r="J88" t="str">
         <x:v>SteriGenix</x:v>
       </x:c>
-      <x:c r="K88" t="str">
-        <x:v>2026-08-26</x:v>
+      <x:c r="K88" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L88" t="str">
         <x:v>Blue</x:v>
@@ -24267,7 +24788,7 @@
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N88" t="str">
-        <x:v>Identity confirmed as GHK-Cu (Copper Peptide) by LC-MS. Blue lyophilized powder; molecular weight matched 402.92 g/mol. Endotoxin PASS; microbial sterility: No Growth; lead, cadmium, arsenic, and mercury Negative. Batch conformity was not tested. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -24275,25 +24796,25 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B89" t="str">
-        <x:v>COA-0072</x:v>
+        <x:v>COA-0074</x:v>
       </x:c>
       <x:c r="C89" t="str">
-        <x:v>KPV</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D89" t="str">
-        <x:v>Healing / Anti-Inflammatory Research</x:v>
+        <x:v>Metabolic / Mitochondrial Research</x:v>
       </x:c>
       <x:c r="E89" t="n">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F89" t="n">
-        <x:v>10.23</x:v>
+        <x:v>41.09</x:v>
       </x:c>
       <x:c r="G89" t="n">
-        <x:v>0.02300000000000004</x:v>
+        <x:v>0.027250000000000087</x:v>
       </x:c>
       <x:c r="H89" t="n">
-        <x:v>99.25</x:v>
+        <x:v>99.3</x:v>
       </x:c>
       <x:c r="I89" t="str">
         <x:v>On label</x:v>
@@ -24311,7 +24832,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N89" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.25%; net content 10.23 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code XXW57EWE.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.3%; net content 41.09 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code SQG57YUA.</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -24319,43 +24840,43 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B90" t="str">
-        <x:v>COA-0091</x:v>
+        <x:v>COA-0076</x:v>
       </x:c>
       <x:c r="C90" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="D90" t="str">
-        <x:v>GLP-1 / Weight Research</x:v>
+        <x:v>Cellular / Metabolic Research</x:v>
       </x:c>
       <x:c r="E90" t="n">
-        <x:v>30</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="F90" t="n">
-        <x:v>32.14</x:v>
+        <x:v>1047.39</x:v>
       </x:c>
       <x:c r="G90" t="n">
-        <x:v>0.07133333333333333</x:v>
+        <x:v>0.0473900000000001</x:v>
       </x:c>
       <x:c r="H90" t="n">
-        <x:v>99.233</x:v>
+        <x:v>99.26</x:v>
       </x:c>
       <x:c r="I90" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J90" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>ILS Labs</x:v>
       </x:c>
       <x:c r="K90" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>08/18/2026</x:v>
       </x:c>
       <x:c r="L90" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M90" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N90" t="str">
-        <x:v>Identity confirmed as TRZ by LC-MS; batch average purity 99.233%; batch average net content 32.14 mg. Endotoxin safety screen PASS; arsenic, cadmium, lead, and mercury negative. Vials: 99.307% / 32.51 mg and 99.158% / 31.77 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.26%; net content 1047.39 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code EKUVZRXB.</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -24363,25 +24884,25 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B91" t="str">
-        <x:v>COA-0065</x:v>
+        <x:v>COA-0072</x:v>
       </x:c>
       <x:c r="C91" t="str">
-        <x:v>AOD-9604</x:v>
+        <x:v>KPV</x:v>
       </x:c>
       <x:c r="D91" t="str">
-        <x:v>Metabolic / Fat Loss</x:v>
+        <x:v>Healing / Anti-Inflammatory Research</x:v>
       </x:c>
       <x:c r="E91" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F91" t="n">
-        <x:v>10.28</x:v>
+        <x:v>10.23</x:v>
       </x:c>
       <x:c r="G91" t="n">
-        <x:v>0.027999999999999935</x:v>
+        <x:v>0.02300000000000004</x:v>
       </x:c>
       <x:c r="H91" t="n">
-        <x:v>99.21</x:v>
+        <x:v>99.25</x:v>
       </x:c>
       <x:c r="I91" t="str">
         <x:v>On label</x:v>
@@ -24399,7 +24920,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N91" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.21%; net content 10.28 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code DNPTRN59.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.25%; net content 10.23 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code XXW57EWE.</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -24407,43 +24928,43 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B92" t="str">
-        <x:v>COA-0086</x:v>
+        <x:v>COA-0062</x:v>
       </x:c>
       <x:c r="C92" t="str">
-        <x:v>BPC-157</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D92" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Cosmetic / Recovery</x:v>
       </x:c>
       <x:c r="E92" t="n">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F92" t="n">
-        <x:v>22.06</x:v>
+        <x:v>52.48</x:v>
       </x:c>
       <x:c r="G92" t="n">
-        <x:v>0.10300000000000001</x:v>
+        <x:v>0.0496</x:v>
       </x:c>
       <x:c r="H92" t="n">
-        <x:v>99.16</x:v>
+        <x:v>99.25</x:v>
       </x:c>
       <x:c r="I92" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J92" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K92" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="L92" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M92" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N92" t="str">
-        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.16%; net content 22.06 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.16% / 22.26 mg and 99.15% / 21.85 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
+        <x:v>Identity confirmed as GHK-Cu (Copper Peptide) by LC-MS. Blue lyophilized powder; molecular weight matched 402.92 g/mol. Endotoxin PASS; microbial sterility: No Growth; lead, cadmium, arsenic, and mercury Negative. Batch conformity was not tested. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -24451,43 +24972,43 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B93" t="str">
-        <x:v>COA-0037</x:v>
+        <x:v>COA-0053</x:v>
       </x:c>
       <x:c r="C93" t="str">
-        <x:v>BPC-157 / TB-500 Blend</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D93" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
+        <x:v>Cosmetic / Recovery</x:v>
       </x:c>
       <x:c r="E93" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F93" t="n">
-        <x:v>10.55</x:v>
+        <x:v>100.52</x:v>
       </x:c>
       <x:c r="G93" t="n">
-        <x:v>0.05500000000000007</x:v>
+        <x:v>0.0052</x:v>
       </x:c>
       <x:c r="H93" t="n">
-        <x:v>99.13</x:v>
+        <x:v>99.25</x:v>
       </x:c>
       <x:c r="I93" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J93" t="str">
-        <x:v>SteriGenix</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K93" t="n">
-        <x:v>46239</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="L93" t="str">
-        <x:v>Red</x:v>
+        <x:v>Light Blue</x:v>
       </x:c>
       <x:c r="M93" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N93" t="str">
-        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -24495,43 +25016,43 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B94" t="str">
-        <x:v>COA-0016</x:v>
+        <x:v>COA-0091</x:v>
       </x:c>
       <x:c r="C94" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D94" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>GLP-1 / Weight Research</x:v>
       </x:c>
       <x:c r="E94" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F94" t="n">
-        <x:v>11.38</x:v>
+        <x:v>32.14</x:v>
       </x:c>
       <x:c r="G94" t="n">
-        <x:v>0.1380000000000001</x:v>
+        <x:v>0.07133333333333333</x:v>
       </x:c>
       <x:c r="H94" t="n">
-        <x:v>99.085</x:v>
+        <x:v>99.233</x:v>
       </x:c>
       <x:c r="I94" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J94" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K94" t="n">
-        <x:v>46155</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K94" t="str">
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="L94" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M94" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N94" t="str">
-        <x:v>TB-500 / TB4</x:v>
+        <x:v>Identity confirmed as TRZ by LC-MS; batch average purity 99.233%; batch average net content 32.14 mg. Endotoxin safety screen PASS; arsenic, cadmium, lead, and mercury negative. Vials: 99.307% / 32.51 mg and 99.158% / 31.77 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -24539,25 +25060,25 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B95" t="str">
-        <x:v>COA-0073</x:v>
+        <x:v>COA-0065</x:v>
       </x:c>
       <x:c r="C95" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>AOD-9604</x:v>
       </x:c>
       <x:c r="D95" t="str">
-        <x:v>Metabolic / Mitochondrial Research</x:v>
+        <x:v>Metabolic / Fat Loss</x:v>
       </x:c>
       <x:c r="E95" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F95" t="n">
-        <x:v>10.42</x:v>
+        <x:v>10.28</x:v>
       </x:c>
       <x:c r="G95" t="n">
-        <x:v>0.041999999999999996</x:v>
+        <x:v>0.027999999999999935</x:v>
       </x:c>
       <x:c r="H95" t="n">
-        <x:v>99.08</x:v>
+        <x:v>99.21</x:v>
       </x:c>
       <x:c r="I95" t="str">
         <x:v>On label</x:v>
@@ -24575,7 +25096,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N95" t="str">
-        <x:v>Identity confirmed; HPLC purity 99.08%; net content 10.42 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 26KYBWZX.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.21%; net content 10.28 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code DNPTRN59.</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -24583,43 +25104,43 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B96" t="str">
-        <x:v>COA-0014</x:v>
+        <x:v>COA-0086</x:v>
       </x:c>
       <x:c r="C96" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>BPC-157</x:v>
       </x:c>
       <x:c r="D96" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E96" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F96" t="n">
-        <x:v>11.17</x:v>
+        <x:v>22.06</x:v>
       </x:c>
       <x:c r="G96" t="n">
-        <x:v>0.117</x:v>
+        <x:v>0.10300000000000001</x:v>
       </x:c>
       <x:c r="H96" t="n">
-        <x:v>99.055</x:v>
+        <x:v>99.16</x:v>
       </x:c>
       <x:c r="I96" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J96" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K96" t="n">
-        <x:v>46155</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K96" t="str">
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="L96" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M96" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N96" t="str">
-        <x:v>MS10 / MOTS-C</x:v>
+        <x:v>Identity confirmed by LC-MS; HPLC-UV purity 99.16%; net content 22.06 mg. Endotoxin replicates PASS; PCR found no detectable microbial DNA; ICP-MS elemental impurities passed; no fentanyl detected. Samples: 99.16% / 22.26 mg and 99.15% / 21.85 mg. Original certificate image/PDF absent from supplied ZIP; database transcription retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -24627,43 +25148,43 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B97" t="str">
-        <x:v>COA-0100</x:v>
+        <x:v>COA-0037</x:v>
       </x:c>
       <x:c r="C97" t="str">
-        <x:v>Tesamorelin</x:v>
+        <x:v>BPC-157 / TB-500 Blend</x:v>
       </x:c>
       <x:c r="D97" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
       <x:c r="E97" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F97" t="n">
-        <x:v>11.34</x:v>
+        <x:v>10.55</x:v>
       </x:c>
       <x:c r="G97" t="n">
-        <x:v>0.134</x:v>
+        <x:v>0.05500000000000007</x:v>
       </x:c>
       <x:c r="H97" t="n">
-        <x:v>99.05</x:v>
+        <x:v>99.13</x:v>
       </x:c>
       <x:c r="I97" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J97" t="str">
-        <x:v>Freedom Diagnostics</x:v>
-      </x:c>
-      <x:c r="K97" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K97" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L97" t="str">
-        <x:v>Black</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="M97" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N97" t="str">
-        <x:v>Samples 99.06% / 11.37mg and 99.04% / 11.30mg; reported mean 99.05% / 11.34mg. Endotoxin, microbial PCR and elemental impurities pass; no fentanyl detected.</x:v>
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -24671,28 +25192,28 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B98" t="str">
-        <x:v>COA-0011</x:v>
+        <x:v>COA-0016</x:v>
       </x:c>
       <x:c r="C98" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>TB-500</x:v>
       </x:c>
       <x:c r="D98" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E98" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F98" t="n">
-        <x:v>10.47</x:v>
+        <x:v>11.38</x:v>
       </x:c>
       <x:c r="G98" t="n">
-        <x:v>0.04700000000000006</x:v>
+        <x:v>0.1380000000000001</x:v>
       </x:c>
       <x:c r="H98" t="n">
-        <x:v>99.04</x:v>
+        <x:v>99.085</x:v>
       </x:c>
       <x:c r="I98" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J98" t="str">
         <x:v>Janoshik</x:v>
@@ -24707,7 +25228,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N98" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>TB-500 / TB4</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -24715,25 +25236,25 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B99" t="str">
-        <x:v>COA-0064</x:v>
+        <x:v>COA-0073</x:v>
       </x:c>
       <x:c r="C99" t="str">
-        <x:v>AHK-Cu</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D99" t="str">
-        <x:v>Cosmetic / Skin Research</x:v>
+        <x:v>Metabolic / Mitochondrial Research</x:v>
       </x:c>
       <x:c r="E99" t="n">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F99" t="n">
-        <x:v>51.12</x:v>
+        <x:v>10.42</x:v>
       </x:c>
       <x:c r="G99" t="n">
-        <x:v>0.022399999999999948</x:v>
+        <x:v>0.041999999999999996</x:v>
       </x:c>
       <x:c r="H99" t="n">
-        <x:v>98.64</x:v>
+        <x:v>99.08</x:v>
       </x:c>
       <x:c r="I99" t="str">
         <x:v>On label</x:v>
@@ -24751,7 +25272,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N99" t="str">
-        <x:v>Identity confirmed; HPLC purity 98.64%; net content 51.12 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6ZNHW4J7.</x:v>
+        <x:v>Identity confirmed; HPLC purity 99.08%; net content 10.42 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 26KYBWZX.</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -24759,24 +25280,26 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B100" t="str">
-        <x:v>COA-0017</x:v>
+        <x:v>COA-0014</x:v>
       </x:c>
       <x:c r="C100" t="str">
-        <x:v>BPC-157</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D100" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E100" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F100" t="n">
-        <x:v>5.54</x:v>
+        <x:v>11.17</x:v>
       </x:c>
       <x:c r="G100" t="n">
-        <x:v>0.108</x:v>
-      </x:c>
-      <x:c r="H100"/>
+        <x:v>0.117</x:v>
+      </x:c>
+      <x:c r="H100" t="n">
+        <x:v>99.055</x:v>
+      </x:c>
       <x:c r="I100" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
@@ -24784,7 +25307,7 @@
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K100" t="n">
-        <x:v>46057</x:v>
+        <x:v>46155</x:v>
       </x:c>
       <x:c r="L100" t="str">
         <x:v>Not Listed</x:v>
@@ -24793,7 +25316,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N100" t="str">
-        <x:v>Blend report BPC5+TB5</x:v>
+        <x:v>MS10 / MOTS-C</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -24801,41 +25324,43 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B101" t="str">
-        <x:v>COA-0018</x:v>
+        <x:v>COA-0100</x:v>
       </x:c>
       <x:c r="C101" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>Tesamorelin</x:v>
       </x:c>
       <x:c r="D101" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E101" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F101" t="n">
-        <x:v>5.43</x:v>
+        <x:v>11.34</x:v>
       </x:c>
       <x:c r="G101" t="n">
-        <x:v>0.08599999999999994</x:v>
-      </x:c>
-      <x:c r="H101"/>
+        <x:v>0.134</x:v>
+      </x:c>
+      <x:c r="H101" t="n">
+        <x:v>99.05</x:v>
+      </x:c>
       <x:c r="I101" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J101" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K101" t="n">
-        <x:v>46057</x:v>
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K101" t="str">
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="L101" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M101" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N101" t="str">
-        <x:v>Blend report BPC5+TB5</x:v>
+        <x:v>Samples 99.06% / 11.37mg and 99.04% / 11.30mg; reported mean 99.05% / 11.34mg. Endotoxin, microbial PCR and elemental impurities pass; no fentanyl detected.</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -24843,34 +25368,206 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B102" t="str">
+        <x:v>COA-0011</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>Cagrilintide</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="E102" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F102" t="n">
+        <x:v>10.47</x:v>
+      </x:c>
+      <x:c r="G102" t="n">
+        <x:v>0.04700000000000006</x:v>
+      </x:c>
+      <x:c r="H102" t="n">
+        <x:v>99.04</x:v>
+      </x:c>
+      <x:c r="I102" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J102" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K102" t="n">
+        <x:v>46155</x:v>
+      </x:c>
+      <x:c r="L102" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M102" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N102" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>COA-0064</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>AHK-Cu</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>Cosmetic / Skin Research</x:v>
+      </x:c>
+      <x:c r="E103" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F103" t="n">
+        <x:v>51.12</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>0.022399999999999948</x:v>
+      </x:c>
+      <x:c r="H103" t="n">
+        <x:v>98.64</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>ILS Labs</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>08/17/2026</x:v>
+      </x:c>
+      <x:c r="L103" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M103" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N103" t="str">
+        <x:v>Identity confirmed; HPLC purity 98.64%; net content 51.12 mg. Heavy metals PASS/not detected; sterility PCR: No Growth; endotoxin reported below commonly referenced thresholds. ILS access code 6ZNHW4J7.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>COA-0018</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>TB-500</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E104" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F104" t="n">
+        <x:v>5.43</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>0.08599999999999994</x:v>
+      </x:c>
+      <x:c r="H104"/>
+      <x:c r="I104" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K104" t="n">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L104" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M104" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N104" t="str">
+        <x:v>Blend report BPC5+TB5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>COA-0017</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E105" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F105" t="n">
+        <x:v>5.54</x:v>
+      </x:c>
+      <x:c r="G105" t="n">
+        <x:v>0.108</x:v>
+      </x:c>
+      <x:c r="H105"/>
+      <x:c r="I105" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J105" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K105" t="n">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L105" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M105" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N105" t="str">
+        <x:v>Blend report BPC5+TB5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
         <x:v>COA-0095</x:v>
       </x:c>
-      <x:c r="C102" t="str">
+      <x:c r="C106" t="str">
         <x:v>hCG 5000 IU</x:v>
       </x:c>
-      <x:c r="D102" t="str">
+      <x:c r="D106" t="str">
         <x:v>Hormone Research</x:v>
       </x:c>
-      <x:c r="E102"/>
-      <x:c r="F102"/>
-      <x:c r="G102"/>
-      <x:c r="H102"/>
-      <x:c r="I102" t="str">
+      <x:c r="E106"/>
+      <x:c r="F106"/>
+      <x:c r="G106"/>
+      <x:c r="H106"/>
+      <x:c r="I106" t="str">
         <x:v>Review (IU; see notes)</x:v>
       </x:c>
-      <x:c r="J102" t="str">
+      <x:c r="J106" t="str">
         <x:v>Chromate</x:v>
       </x:c>
-      <x:c r="K102" t="str">
+      <x:c r="K106" t="str">
         <x:v>2026-10-12</x:v>
       </x:c>
-      <x:c r="L102" t="str">
+      <x:c r="L106" t="str">
         <x:v>Red</x:v>
       </x:c>
-      <x:c r="M102" t="str">
+      <x:c r="M106" t="str">
         <x:v>Silver</x:v>
       </x:c>
-      <x:c r="N102" t="str">
+      <x:c r="N106" t="str">
         <x:v>Labeled quantity 5000 IU; measured quantity 6288 IU (25.76% above label). These are IU, NOT mg; mg fields deliberately blank. HPLC-UV potency estimate has approximately +/-15% margin of error. Purity not reported. Identity: hCG. Received 2026-09-29.</x:v>
       </x:c>
     </x:row>
@@ -33815,6 +34512,278 @@
         <x:v>Purple cap / silver crimp visible or listed in supplied report.</x:v>
       </x:c>
     </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D103" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E103" t="n">
+        <x:v>113.38</x:v>
+      </x:c>
+      <x:c r="F103" t="n">
+        <x:v>13.38</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>0.1338</x:v>
+      </x:c>
+      <x:c r="H103" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L103" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="M103" t="str">
+        <x:v>2610190479</x:v>
+      </x:c>
+      <x:c r="N103" t="str">
+        <x:v>RTPe2610190479</x:v>
+      </x:c>
+      <x:c r="O103" t="str">
+        <x:v>Light Blue Cap</x:v>
+      </x:c>
+      <x:c r="P103" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="Q103" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R103" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S103" t="str">
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+      <x:c r="T103" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U103" t="str">
+        <x:v>Light Blue</x:v>
+      </x:c>
+      <x:c r="V103" t="str">
+        <x:v>Cap: Light Blue; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Cellular Support</x:v>
+      </x:c>
+      <x:c r="D104" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E104" t="n">
+        <x:v>1054.63</x:v>
+      </x:c>
+      <x:c r="F104" t="n">
+        <x:v>54.63</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>0.054630000000000005</x:v>
+      </x:c>
+      <x:c r="H104" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K104" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L104" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="M104" t="str">
+        <x:v>2610190475</x:v>
+      </x:c>
+      <x:c r="N104" t="str">
+        <x:v>RTPe2610190475</x:v>
+      </x:c>
+      <x:c r="O104" t="str">
+        <x:v>White Cap</x:v>
+      </x:c>
+      <x:c r="P104" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/nad-plus/NAD-1000mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="Q104" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R104" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S104" t="str">
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+      <x:c r="T104" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U104" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="V104" t="str">
+        <x:v>Cap: White; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D105" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E105" t="n">
+        <x:v>10.94</x:v>
+      </x:c>
+      <x:c r="F105" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="G105" t="n">
+        <x:v>0.094</x:v>
+      </x:c>
+      <x:c r="H105" t="n">
+        <x:v>99.3905</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J105" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K105" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L105" t="str">
+        <x:v>2026-10-27</x:v>
+      </x:c>
+      <x:c r="M105" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N105" t="str">
+        <x:v>BYFJEIELXUE7</x:v>
+      </x:c>
+      <x:c r="O105" t="str">
+        <x:v>RE10-2610RT</x:v>
+      </x:c>
+      <x:c r="P105" t="str">
+        <x:v>assets/coa/images/janoshik/retatrutide/Retatrutide-10mg-2026-10-27.jpg</x:v>
+      </x:c>
+      <x:c r="Q105" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R105" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S105" t="str">
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
+      </x:c>
+      <x:c r="T105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="V105" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D106" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E106" t="n">
+        <x:v>12.76</x:v>
+      </x:c>
+      <x:c r="F106" t="n">
+        <x:v>2.76</x:v>
+      </x:c>
+      <x:c r="G106" t="n">
+        <x:v>0.27599999999999997</x:v>
+      </x:c>
+      <x:c r="H106" t="n">
+        <x:v>99.51</x:v>
+      </x:c>
+      <x:c r="I106" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J106" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K106" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="L106" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="M106" t="str">
+        <x:v>RT10-20260918S2146</x:v>
+      </x:c>
+      <x:c r="N106" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="O106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="P106" t="str">
+        <x:v>assets/coa/documents/tianjin-qiangxin/retatrutide/RT10-20260918S2146_report.pdf</x:v>
+      </x:c>
+      <x:c r="Q106" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R106" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+      <x:c r="S106" t="str">
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
+      </x:c>
+      <x:c r="T106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="V106" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -35482,10 +36451,8 @@
           <x:t xml:space="preserve">Freedom Diagnostics</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GHK-Cu, KLOW 80mg, Retatrutide</x:t>
-        </x:is>
+      <x:c r="B4" t="str">
+        <x:v>GHK-Cu, KLOW 80mg, Retatrutide, NAD+</x:v>
       </x:c>
       <x:c r="C4" t="inlineStr">
         <x:is>
@@ -35614,10 +36581,8 @@
           <x:t xml:space="preserve">Tianjin Qiangxin (third-party partner lab)</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Eloralintide</x:t>
-        </x:is>
+      <x:c r="B10" t="str">
+        <x:v>Eloralintide, Retatrutide</x:v>
       </x:c>
       <x:c r="C10" t="inlineStr">
         <x:is>
@@ -43507,6 +44472,254 @@
         <x:v>Reported 2026-10-14. BPC-157 acetate; HPLC VWD SOP-043: potency 24.36%, 243.62mg/g, 19.66mg/unit. Expanded uncertainty +/-7.81% at 95% confidence. No sterility or endotoxin results supplied.</x:v>
       </x:c>
     </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D103" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E103" t="n">
+        <x:v>113.38</x:v>
+      </x:c>
+      <x:c r="F103" t="n">
+        <x:v>13.38</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>0.1338</x:v>
+      </x:c>
+      <x:c r="H103" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>Light Blue Cap</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L103" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="M103" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+      <x:c r="N103" t="str">
+        <x:v>2610190479</x:v>
+      </x:c>
+      <x:c r="O103" t="str">
+        <x:v>RTPe2610190479</x:v>
+      </x:c>
+      <x:c r="P103" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="Q103" t="str">
+        <x:v>Light Blue</x:v>
+      </x:c>
+      <x:c r="R103" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="S103" t="str">
+        <x:v>Cap: Light Blue; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="T103" t="str">
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Cellular Support</x:v>
+      </x:c>
+      <x:c r="D104" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E104" t="n">
+        <x:v>1054.63</x:v>
+      </x:c>
+      <x:c r="F104" t="n">
+        <x:v>54.63</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>0.054630000000000005</x:v>
+      </x:c>
+      <x:c r="H104" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>White Cap</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="K104" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L104" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="M104" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+      <x:c r="N104" t="str">
+        <x:v>2610190475</x:v>
+      </x:c>
+      <x:c r="O104" t="str">
+        <x:v>RTPe2610190475</x:v>
+      </x:c>
+      <x:c r="P104" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/nad-plus/NAD-1000mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="Q104" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="R104" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="S104" t="str">
+        <x:v>Cap: White; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="T104" t="str">
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D105" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E105" t="n">
+        <x:v>10.94</x:v>
+      </x:c>
+      <x:c r="F105" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="G105" t="n">
+        <x:v>0.094</x:v>
+      </x:c>
+      <x:c r="H105" t="n">
+        <x:v>99.3905</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>RE10-2610RT</x:v>
+      </x:c>
+      <x:c r="J105" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K105" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L105" t="str">
+        <x:v>2026-10-27</x:v>
+      </x:c>
+      <x:c r="M105" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+      <x:c r="N105" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O105" t="str">
+        <x:v>BYFJEIELXUE7</x:v>
+      </x:c>
+      <x:c r="P105" t="str">
+        <x:v>assets/coa/images/janoshik/retatrutide/Retatrutide-10mg-2026-10-27.jpg</x:v>
+      </x:c>
+      <x:c r="Q105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="R105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="S105" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="T105" t="str">
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D106" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E106" t="n">
+        <x:v>12.76</x:v>
+      </x:c>
+      <x:c r="F106" t="n">
+        <x:v>2.76</x:v>
+      </x:c>
+      <x:c r="G106" t="n">
+        <x:v>0.27599999999999997</x:v>
+      </x:c>
+      <x:c r="H106" t="n">
+        <x:v>99.51</x:v>
+      </x:c>
+      <x:c r="I106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="J106" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K106" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L106" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="M106" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+      <x:c r="N106" t="str">
+        <x:v>RT10-20260918S2146</x:v>
+      </x:c>
+      <x:c r="O106" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="P106" t="str">
+        <x:v>assets/coa/documents/tianjin-qiangxin/retatrutide/RT10-20260918S2146_report.pdf</x:v>
+      </x:c>
+      <x:c r="Q106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="R106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="S106" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+      <x:c r="T106" t="str">
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -51967,6 +53180,266 @@
         <x:v>Purple cap / silver crimp visible or listed in supplied report.</x:v>
       </x:c>
     </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>2610190479</x:v>
+      </x:c>
+      <x:c r="F103" t="str">
+        <x:v>RTPe2610190479</x:v>
+      </x:c>
+      <x:c r="G103" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="H103" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="I103" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J103" t="n">
+        <x:v>113.38</x:v>
+      </x:c>
+      <x:c r="K103" t="n">
+        <x:v>13.38</x:v>
+      </x:c>
+      <x:c r="L103" t="n">
+        <x:v>0.1338</x:v>
+      </x:c>
+      <x:c r="M103" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="N103" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O103" t="str">
+        <x:v>Light Blue Cap</x:v>
+      </x:c>
+      <x:c r="P103" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="Q103" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R103" t="str">
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+      <x:c r="S103" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="T103" t="str">
+        <x:v>Light Blue</x:v>
+      </x:c>
+      <x:c r="U103" t="str">
+        <x:v>Cap: Light Blue; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Cellular Support</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+      <x:c r="E104" t="str">
+        <x:v>2610190475</x:v>
+      </x:c>
+      <x:c r="F104" t="str">
+        <x:v>RTPe2610190475</x:v>
+      </x:c>
+      <x:c r="G104" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/nad-plus/NAD-1000mg-2026-10-20.jpg</x:v>
+      </x:c>
+      <x:c r="H104" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="I104" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="J104" t="n">
+        <x:v>1054.63</x:v>
+      </x:c>
+      <x:c r="K104" t="n">
+        <x:v>54.63</x:v>
+      </x:c>
+      <x:c r="L104" t="n">
+        <x:v>0.054630000000000005</x:v>
+      </x:c>
+      <x:c r="M104" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+      <x:c r="N104" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O104" t="str">
+        <x:v>White Cap</x:v>
+      </x:c>
+      <x:c r="P104" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="Q104" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R104" t="str">
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+      <x:c r="S104" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="T104" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="U104" t="str">
+        <x:v>Cap: White; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="E105" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="F105" t="str">
+        <x:v>BYFJEIELXUE7</x:v>
+      </x:c>
+      <x:c r="G105" t="str">
+        <x:v>assets/coa/images/janoshik/retatrutide/Retatrutide-10mg-2026-10-27.jpg</x:v>
+      </x:c>
+      <x:c r="H105" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="I105" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J105" t="n">
+        <x:v>10.94</x:v>
+      </x:c>
+      <x:c r="K105" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="L105" t="n">
+        <x:v>0.094</x:v>
+      </x:c>
+      <x:c r="M105" t="n">
+        <x:v>99.3905</x:v>
+      </x:c>
+      <x:c r="N105" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O105" t="str">
+        <x:v>RE10-2610RT</x:v>
+      </x:c>
+      <x:c r="P105" t="str">
+        <x:v>2026-10-27</x:v>
+      </x:c>
+      <x:c r="Q105" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R105" t="str">
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
+      </x:c>
+      <x:c r="S105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="T105" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U105" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D106" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="E106" t="str">
+        <x:v>RT10-20260918S2146</x:v>
+      </x:c>
+      <x:c r="F106" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="G106" t="str">
+        <x:v>assets/coa/documents/tianjin-qiangxin/retatrutide/RT10-20260918S2146_report.pdf</x:v>
+      </x:c>
+      <x:c r="H106" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+      <x:c r="I106" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J106" t="n">
+        <x:v>12.76</x:v>
+      </x:c>
+      <x:c r="K106" t="n">
+        <x:v>2.76</x:v>
+      </x:c>
+      <x:c r="L106" t="n">
+        <x:v>0.27599999999999997</x:v>
+      </x:c>
+      <x:c r="M106" t="n">
+        <x:v>99.51</x:v>
+      </x:c>
+      <x:c r="N106" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="P106" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="Q106" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+      <x:c r="R106" t="str">
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
+      </x:c>
+      <x:c r="S106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="T106" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+      <x:c r="U106" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -54755,6 +56228,794 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="65" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Compound</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>113.38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Variance (mg)</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>13.38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Variance %</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>0.1338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Lab Match</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>2610190479</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>RTPe2610190479</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Light Blue Cap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Source Type</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-10-20.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>Pass/Fail</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Duplicate Handling</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Sample 1: 99.98%, 114.55 mg; sample 2: 99.99%, 112.21 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Light Blue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>Closure Notes</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Cap: Light Blue; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="65" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Compound</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Cellular Support</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>1054.63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Variance (mg)</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>54.63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Variance %</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>0.054630000000000005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>99.99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Freedom Diagnostics</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Lab Match</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>2610190475</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>RTPe2610190475</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>White Cap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Source Type</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/images/freedom-diagnostics/nad-plus/NAD-1000mg-2026-10-20.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>Pass/Fail</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Duplicate Handling</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Sample 1: 99.99%, 1058.75 mg; sample 2: 99.99%, 1050.51 mg. Identity confirmed. Endotoxin replicates pass; sensitivity ≤0.05 EU/mL. Received 2026-10-19; reported 2026-10-20. Endotoxin results only; overall pass/fail not stated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>White</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>Closure Notes</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Cap: White; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="65" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Compound</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>10.94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Variance (mg)</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Variance %</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>0.094</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>99.3905</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Lab Match</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>2026-10-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>BYFJEIELXUE7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>RE10-2610RT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Source Type</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/images/janoshik/retatrutide/Retatrutide-10mg-2026-10-27.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>Pass/Fail</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Duplicate Handling</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Two results: 11.04 mg / 99.342% and 10.84 mg / 99.439%. Displayed content and purity are calculated averages, not separately reported values. Ordered 2026-10-19; received 2026-10-23. Cap color not clearly identified; image is cropped. Task number redacted.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>Closure Notes</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="65" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Compound</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>12.76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Variance (mg)</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>2.76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Variance %</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>0.27599999999999997</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>99.51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Lab Match</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Not independently verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>RT10-20260918S2146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Source Type</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/documents/tianjin-qiangxin/retatrutide/RT10-20260918S2146_report.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>Pass/Fail</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Not Reported</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Duplicate Handling</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Unique supplied report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Four-page report: purity 99.51%, content 12.76 mg, mass spectrum detected. Report states testing performed by a third-party partner; neither party holds CMA/CNAS accreditation. Authentication code blank. Cap color not reported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Not listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>Closure Notes</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Cap: Not listed; crimp: Not listed.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
